--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -747,17 +747,17 @@
         <v>46083</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.659722222222222</v>
+        <v>0.739583333333333</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">(D6-C6-E6)*24</f>
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="G6" s="12"/>
     </row>
@@ -769,10 +769,10 @@
         <v>46084</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.6875</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0.0208333333333333</v>
@@ -791,17 +791,17 @@
         <v>46085</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.652777777777778</v>
+        <v>0.711805555555556</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">(D8-C8-E8)*24</f>
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="G8" s="12"/>
     </row>
@@ -813,17 +813,17 @@
         <v>46086</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.715277777777778</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">(D9-C9-E9)*24</f>
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="G9" s="12"/>
     </row>
@@ -835,17 +835,17 @@
         <v>46087</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.638888888888889</v>
+        <v>0.736111111111111</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">(D10-C10-E10)*24</f>
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
       <c r="G10" s="12"/>
     </row>
@@ -887,17 +887,17 @@
         <v>46090</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.3125</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.666666666666667</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">(D13-C13-E13)*24</f>
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="G13" s="12"/>
     </row>
@@ -909,17 +909,17 @@
         <v>46091</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.302083333333333</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.729166666666667</v>
+        <v>0.690972222222222</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">(D14-C14-E14)*24</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G14" s="12"/>
     </row>
@@ -931,17 +931,17 @@
         <v>46092</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.645833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">(D15-C15-E15)*24</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" s="12"/>
     </row>
@@ -953,17 +953,17 @@
         <v>46093</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.669444444444444</v>
+        <v>0.71875</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">(D16-C16-E16)*24</f>
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="12"/>
     </row>
@@ -975,17 +975,17 @@
         <v>46094</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.305555555555556</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.713888888888889</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">(D17-C17-E17)*24</f>
-        <v>9.05</v>
+        <v>9.5</v>
       </c>
       <c r="G17" s="12"/>
     </row>
@@ -1027,17 +1027,17 @@
         <v>46097</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.652777777777778</v>
+        <v>0.736111111111111</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">(D20-C20-E20)*24</f>
-        <v>8.3</v>
+        <v>9.75</v>
       </c>
       <c r="G20" s="12"/>
     </row>
@@ -1049,17 +1049,17 @@
         <v>46098</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.632638888888889</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">(D21-C21-E21)*24</f>
-        <v>7.55</v>
+        <v>9.25</v>
       </c>
       <c r="G21" s="12"/>
     </row>
@@ -1071,17 +1071,17 @@
         <v>46099</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>0.5</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.739583333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">(D22-C22-E22)*24</f>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>19</v>
@@ -1095,17 +1095,17 @@
         <v>46100</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.672222222222222</v>
+        <v>0.711805555555556</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F23" s="11" t="n">
         <f aca="false">(D23-C23-E23)*24</f>
-        <v>8.8</v>
+        <v>9.25</v>
       </c>
       <c r="G23" s="12"/>
     </row>
@@ -1162,17 +1162,17 @@
         <v>46104</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.70625</v>
+        <v>0.75</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F27" s="11" t="n">
         <f aca="false">(D27-C27-E27)*24</f>
-        <v>9.2</v>
+        <v>9.75</v>
       </c>
       <c r="G27" s="12"/>
     </row>
@@ -1184,17 +1184,17 @@
         <v>46105</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.661111111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">(D28-C28-E28)*24</f>
-        <v>8.45</v>
+        <v>10</v>
       </c>
       <c r="G28" s="12"/>
     </row>
@@ -1206,10 +1206,10 @@
         <v>46106</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>0.506944444444444</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.725694444444444</v>
+        <v>0.708333333333333</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.0104166666666667</v>
@@ -1230,17 +1230,17 @@
         <v>46107</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.692361111111111</v>
+        <v>0.6875</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F30" s="11" t="n">
         <f aca="false">(D30-C30-E30)*24</f>
-        <v>8.95</v>
+        <v>9</v>
       </c>
       <c r="G30" s="12"/>
     </row>
@@ -1252,10 +1252,10 @@
         <v>46108</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.690972222222222</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.0208333333333333</v>
@@ -1304,17 +1304,17 @@
         <v>46111</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.629166666666667</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F34" s="11" t="n">
         <f aca="false">(D34-C34-E34)*24</f>
-        <v>7.85</v>
+        <v>10</v>
       </c>
       <c r="G34" s="12"/>
     </row>
@@ -1326,17 +1326,17 @@
         <v>46112</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>0.302083333333333</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.664583333333333</v>
+        <v>0.732638888888889</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F35" s="11" t="n">
         <f aca="false">(D35-C35-E35)*24</f>
-        <v>8.2</v>
+        <v>9.5</v>
       </c>
       <c r="G35" s="12"/>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F36" s="17" t="n">
         <f aca="false">SUM(F5:F35)</f>
-        <v>173.45</v>
+        <v>191.5</v>
       </c>
       <c r="G36" s="18" t="s">
         <v>22</v>
@@ -1459,17 +1459,17 @@
         <v>46113</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.496527777777778</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.725694444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">(D5-C5-E5)*24</f>
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>19</v>
@@ -1486,14 +1486,14 @@
         <v>0.291666666666667</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.716666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">(D6-C6-E6)*24</f>
-        <v>9.45</v>
+        <v>10.25</v>
       </c>
       <c r="G6" s="12"/>
     </row>
@@ -1565,17 +1565,17 @@
         <v>46119</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.3125</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.648611111111111</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">(D11-C11-E11)*24</f>
-        <v>8.1</v>
+        <v>9.25</v>
       </c>
       <c r="G11" s="12"/>
     </row>
@@ -1587,17 +1587,17 @@
         <v>46120</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.510416666666667</v>
+        <v>0.496527777777778</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.760416666666667</v>
+        <v>0.715277777777778</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">(D12-C12-E12)*24</f>
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>19</v>
@@ -1611,17 +1611,17 @@
         <v>46121</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0.305555555555556</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.688888888888889</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">(D13-C13-E13)*24</f>
-        <v>8.7</v>
+        <v>9.5</v>
       </c>
       <c r="G13" s="12"/>
     </row>
@@ -1633,17 +1633,17 @@
         <v>46122</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.704861111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">(D14-C14-E14)*24</f>
-        <v>9.3</v>
+        <v>10</v>
       </c>
       <c r="G14" s="12"/>
     </row>
@@ -1685,17 +1685,17 @@
         <v>46125</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.653472222222222</v>
+        <v>0.739583333333333</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">(D17-C17-E17)*24</f>
-        <v>8.05</v>
+        <v>10</v>
       </c>
       <c r="G17" s="12"/>
     </row>
@@ -1707,17 +1707,17 @@
         <v>46126</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.661805555555556</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">(D18-C18-E18)*24</f>
-        <v>8.55</v>
+        <v>9.5</v>
       </c>
       <c r="G18" s="12"/>
     </row>
@@ -1732,14 +1732,14 @@
         <v>0.503472222222222</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.711805555555556</v>
+        <v>0.732638888888889</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">(D19-C19-E19)*24</f>
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>19</v>
@@ -1753,17 +1753,17 @@
         <v>46128</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.704166666666667</v>
+        <v>0.715277777777778</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">(D20-C20-E20)*24</f>
-        <v>9.15</v>
+        <v>9.25</v>
       </c>
       <c r="G20" s="12"/>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46129</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.640277777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">(D21-C21-E21)*24</f>
-        <v>7.95</v>
+        <v>10.25</v>
       </c>
       <c r="G21" s="12"/>
     </row>
@@ -1827,17 +1827,17 @@
         <v>46132</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.667361111111111</v>
+        <v>0.732638888888889</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F24" s="11" t="n">
         <f aca="false">(D24-C24-E24)*24</f>
-        <v>8.35</v>
+        <v>9.75</v>
       </c>
       <c r="G24" s="12"/>
     </row>
@@ -1849,17 +1849,17 @@
         <v>46133</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.715972222222222</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F25" s="11" t="n">
         <f aca="false">(D25-C25-E25)*24</f>
-        <v>9.35</v>
+        <v>9.75</v>
       </c>
       <c r="G25" s="12"/>
     </row>
@@ -1871,17 +1871,17 @@
         <v>46134</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.5</v>
+        <v>0.493055555555556</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.71875</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F26" s="11" t="n">
         <f aca="false">(D26-C26-E26)*24</f>
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>19</v>
@@ -1895,17 +1895,17 @@
         <v>46135</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.6625</v>
+        <v>0.75</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F27" s="11" t="n">
         <f aca="false">(D27-C27-E27)*24</f>
-        <v>8.65</v>
+        <v>10</v>
       </c>
       <c r="G27" s="12"/>
     </row>
@@ -1917,17 +1917,17 @@
         <v>46136</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.302083333333333</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.677083333333333</v>
+        <v>0.71875</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">(D28-C28-E28)*24</f>
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="G28" s="12"/>
     </row>
@@ -1969,17 +1969,17 @@
         <v>46139</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.6875</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">(D31-C31-E31)*24</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G31" s="12"/>
     </row>
@@ -1991,17 +1991,17 @@
         <v>46140</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.654861111111111</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F32" s="11" t="n">
         <f aca="false">(D32-C32-E32)*24</f>
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="G32" s="12"/>
     </row>
@@ -2013,17 +2013,17 @@
         <v>46141</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.506944444444444</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.750694444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F33" s="11" t="n">
         <f aca="false">(D33-C33-E33)*24</f>
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>19</v>
@@ -2040,14 +2040,14 @@
         <v>0.305555555555556</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.722222222222222</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F34" s="11" t="n">
         <f aca="false">(D34-C34-E34)*24</f>
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="G34" s="12"/>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">SUM(F5:F34)</f>
-        <v>156.95</v>
+        <v>173.75</v>
       </c>
       <c r="G35" s="18" t="s">
         <v>22</v>
@@ -2215,17 +2215,17 @@
         <v>46146</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.629861111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">(D8-C8-E8)*24</f>
-        <v>7.75</v>
+        <v>10.25</v>
       </c>
       <c r="G8" s="12"/>
     </row>
@@ -2237,17 +2237,17 @@
         <v>46147</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.3125</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.682638888888889</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">(D9-C9-E9)*24</f>
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="G9" s="12"/>
     </row>
@@ -2259,17 +2259,17 @@
         <v>46148</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.496527777777778</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.727777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">(D10-C10-E10)*24</f>
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>19</v>
@@ -2283,10 +2283,10 @@
         <v>46149</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.711805555555556</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0.03125</v>
@@ -2305,17 +2305,17 @@
         <v>46150</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.645833333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">(D12-C12-E12)*24</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G12" s="12"/>
     </row>
@@ -2357,17 +2357,17 @@
         <v>46153</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.667361111111111</v>
+        <v>0.739583333333333</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">(D15-C15-E15)*24</f>
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="G15" s="12"/>
     </row>
@@ -2379,17 +2379,17 @@
         <v>46154</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.706944444444445</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">(D16-C16-E16)*24</f>
-        <v>9.05</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="12"/>
     </row>
@@ -2401,17 +2401,17 @@
         <v>46155</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.510416666666667</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.752083333333333</v>
+        <v>0.708333333333333</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">(D17-C17-E17)*24</f>
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>19</v>
@@ -2440,17 +2440,17 @@
         <v>46157</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.661805555555556</v>
+        <v>0.715277777777778</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">(D19-C19-E19)*24</f>
-        <v>8.3</v>
+        <v>9.25</v>
       </c>
       <c r="G19" s="12"/>
     </row>
@@ -2492,17 +2492,17 @@
         <v>46160</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.616666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">(D22-C22-E22)*24</f>
-        <v>7.55</v>
+        <v>10.25</v>
       </c>
       <c r="G22" s="12"/>
     </row>
@@ -2514,17 +2514,17 @@
         <v>46161</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0.302083333333333</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.689583333333333</v>
+        <v>0.732638888888889</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F23" s="11" t="n">
         <f aca="false">(D23-C23-E23)*24</f>
-        <v>8.8</v>
+        <v>9.75</v>
       </c>
       <c r="G23" s="12"/>
     </row>
@@ -2539,14 +2539,14 @@
         <v>0.503472222222222</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.718055555555556</v>
+        <v>0.732638888888889</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F24" s="11" t="n">
         <f aca="false">(D24-C24-E24)*24</f>
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>19</v>
@@ -2560,17 +2560,17 @@
         <v>46163</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.70625</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0.03125</v>
       </c>
       <c r="F25" s="11" t="n">
         <f aca="false">(D25-C25-E25)*24</f>
-        <v>9.2</v>
+        <v>9.75</v>
       </c>
       <c r="G25" s="12"/>
     </row>
@@ -2582,17 +2582,17 @@
         <v>46164</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.663194444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F26" s="11" t="n">
         <f aca="false">(D26-C26-E26)*24</f>
-        <v>8.45</v>
+        <v>10</v>
       </c>
       <c r="G26" s="12"/>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46168</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.305555555555556</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.699305555555556</v>
+        <v>0.71875</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F30" s="11" t="n">
         <f aca="false">(D30-C30-E30)*24</f>
-        <v>8.95</v>
+        <v>9.5</v>
       </c>
       <c r="G30" s="12"/>
     </row>
@@ -2674,14 +2674,14 @@
         <v>0.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.735416666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">(D31-C31-E31)*24</f>
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>19</v>
@@ -2695,17 +2695,17 @@
         <v>46170</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.681944444444445</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F32" s="11" t="n">
         <f aca="false">(D32-C32-E32)*24</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G32" s="12"/>
     </row>
@@ -2717,17 +2717,17 @@
         <v>46171</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.645138888888889</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F33" s="11" t="n">
         <f aca="false">(D33-C33-E33)*24</f>
-        <v>7.85</v>
+        <v>10</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F36" s="17" t="n">
         <f aca="false">SUM(F5:F35)</f>
-        <v>140.9</v>
+        <v>158.5</v>
       </c>
       <c r="G36" s="18" t="s">
         <v>22</v>
@@ -2880,17 +2880,17 @@
         <v>46174</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.647222222222222</v>
+        <v>0.670138888888889</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">(D5-C5-E5)*24</f>
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="G5" s="12"/>
     </row>
@@ -2902,17 +2902,17 @@
         <v>46175</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.716666666666667</v>
+        <v>0.621527777777778</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">(D6-C6-E6)*24</f>
-        <v>9.45</v>
+        <v>7.25</v>
       </c>
       <c r="G6" s="12"/>
     </row>
@@ -2924,17 +2924,17 @@
         <v>46176</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.506944444444444</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.731944444444444</v>
+        <v>0.75</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">(D7-C7-E7)*24</f>
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>19</v>
@@ -2963,17 +2963,17 @@
         <v>46178</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.3125</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.646527777777778</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">(D9-C9-E9)*24</f>
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G9" s="12"/>
     </row>
@@ -3015,17 +3015,17 @@
         <v>46181</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.681944444444445</v>
+        <v>0.649305555555556</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">(D12-C12-E12)*24</f>
-        <v>8.7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="12"/>
     </row>
@@ -3037,17 +3037,17 @@
         <v>46182</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.309027777777778</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.713888888888889</v>
+        <v>0.663194444444444</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">(D13-C13-E13)*24</f>
-        <v>9.3</v>
+        <v>8</v>
       </c>
       <c r="G13" s="12"/>
     </row>
@@ -3059,17 +3059,17 @@
         <v>46183</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.496527777777778</v>
+        <v>0.506944444444444</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.736111111111111</v>
+        <v>0.725694444444444</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">(D14-C14-E14)*24</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>19</v>
@@ -3083,17 +3083,17 @@
         <v>46184</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.6375</v>
+        <v>0.625</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">(D15-C15-E15)*24</f>
-        <v>8.05</v>
+        <v>7.5</v>
       </c>
       <c r="G15" s="12"/>
     </row>
@@ -3108,14 +3108,14 @@
         <v>0.302083333333333</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.679166666666667</v>
+        <v>0.625</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">(D16-C16-E16)*24</f>
-        <v>8.55</v>
+        <v>7.25</v>
       </c>
       <c r="G16" s="12"/>
     </row>
@@ -3157,17 +3157,17 @@
         <v>46188</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.704166666666667</v>
+        <v>0.663194444444444</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">(D19-C19-E19)*24</f>
-        <v>9.15</v>
+        <v>8.25</v>
       </c>
       <c r="G19" s="12"/>
     </row>
@@ -3179,17 +3179,17 @@
         <v>46189</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.642361111111111</v>
+        <v>0.649305555555556</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">(D20-C20-E20)*24</f>
-        <v>7.95</v>
+        <v>7.75</v>
       </c>
       <c r="G20" s="12"/>
     </row>
@@ -3201,17 +3201,17 @@
         <v>46190</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>0.510416666666667</v>
+        <v>0.496527777777778</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.729166666666667</v>
+        <v>0.725694444444444</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">(D21-C21-E21)*24</f>
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>19</v>
@@ -3225,17 +3225,17 @@
         <v>46191</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>0.305555555555556</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.674305555555556</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">(D22-C22-E22)*24</f>
-        <v>8.35</v>
+        <v>7.75</v>
       </c>
       <c r="G22" s="12"/>
     </row>
@@ -3247,17 +3247,17 @@
         <v>46192</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.3125</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.706944444444445</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F23" s="11" t="n">
         <f aca="false">(D23-C23-E23)*24</f>
-        <v>9.35</v>
+        <v>8</v>
       </c>
       <c r="G23" s="12"/>
     </row>
@@ -3299,17 +3299,17 @@
         <v>46195</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.678472222222222</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F26" s="11" t="n">
         <f aca="false">(D26-C26-E26)*24</f>
-        <v>8.65</v>
+        <v>7.5</v>
       </c>
       <c r="G26" s="12"/>
     </row>
@@ -3321,17 +3321,17 @@
         <v>46196</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.659722222222222</v>
+        <v>0.625</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F27" s="11" t="n">
         <f aca="false">(D27-C27-E27)*24</f>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G27" s="12"/>
     </row>
@@ -3343,17 +3343,17 @@
         <v>46197</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.503472222222222</v>
+        <v>0.5</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.732638888888889</v>
+        <v>0.75</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">(D28-C28-E28)*24</f>
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>19</v>
@@ -3367,17 +3367,17 @@
         <v>46198</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F29" s="11" t="n">
         <f aca="false">(D29-C29-E29)*24</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G29" s="12"/>
     </row>
@@ -3389,10 +3389,10 @@
         <v>46199</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.652777777777778</v>
+        <v>0.659722222222222</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0.0208333333333333</v>
@@ -3441,17 +3441,17 @@
         <v>46202</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.715277777777778</v>
+        <v>0.628472222222222</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F33" s="11" t="n">
         <f aca="false">(D33-C33-E33)*24</f>
-        <v>9.25</v>
+        <v>7.25</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3463,10 +3463,10 @@
         <v>46203</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.638888888888889</v>
+        <v>0.642361111111111</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0.0208333333333333</v>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">SUM(F5:F34)</f>
-        <v>167.45</v>
+        <v>153.75</v>
       </c>
       <c r="G35" s="18" t="s">
         <v>22</v>
@@ -3596,17 +3596,17 @@
         <v>46204</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.493055555555556</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.75</v>
+        <v>0.732638888888889</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.0104166666666667</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">(D5-C5-E5)*24</f>
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>19</v>
@@ -3620,17 +3620,17 @@
         <v>46205</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.3125</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.666666666666667</v>
+        <v>0.614583333333333</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">(D6-C6-E6)*24</f>
-        <v>8.75</v>
+        <v>6.75</v>
       </c>
       <c r="G6" s="12"/>
     </row>
@@ -3687,17 +3687,17 @@
         <v>46209</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.302083333333333</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.729166666666667</v>
+        <v>0.597222222222222</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">(D10-C10-E10)*24</f>
-        <v>9.5</v>
+        <v>6.75</v>
       </c>
       <c r="G10" s="12"/>
     </row>
@@ -3709,17 +3709,17 @@
         <v>46210</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.309027777777778</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.645833333333333</v>
+        <v>0.600694444444444</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">(D11-C11-E11)*24</f>
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G11" s="12"/>
     </row>
@@ -3731,17 +3731,17 @@
         <v>46211</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.669444444444444</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">(D12-C12-E12)*24</f>
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="12"/>
     </row>
@@ -3753,17 +3753,17 @@
         <v>46212</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0.305555555555556</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.713888888888889</v>
+        <v>0.614583333333333</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">(D13-C13-E13)*24</f>
-        <v>9.05</v>
+        <v>7</v>
       </c>
       <c r="G13" s="12"/>
     </row>
@@ -3775,17 +3775,17 @@
         <v>46213</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.652777777777778</v>
+        <v>0.590277777777778</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">(D14-C14-E14)*24</f>
-        <v>8.3</v>
+        <v>6.5</v>
       </c>
       <c r="G14" s="12"/>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46216</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.632638888888889</v>
+        <v>0.607638888888889</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">(D17-C17-E17)*24</f>
-        <v>7.55</v>
+        <v>6.75</v>
       </c>
       <c r="G17" s="12"/>
     </row>
@@ -3849,17 +3849,17 @@
         <v>46217</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.672222222222222</v>
+        <v>0.597222222222222</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">(D18-C18-E18)*24</f>
-        <v>8.8</v>
+        <v>6.75</v>
       </c>
       <c r="G18" s="12"/>
     </row>
@@ -3871,17 +3871,17 @@
         <v>46218</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.70625</v>
+        <v>0.614583333333333</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">(D19-C19-E19)*24</f>
-        <v>9.2</v>
+        <v>6.75</v>
       </c>
       <c r="G19" s="12"/>
     </row>
@@ -3893,17 +3893,17 @@
         <v>46219</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.288194444444444</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.661111111111111</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">(D20-C20-E20)*24</f>
-        <v>8.45</v>
+        <v>6.75</v>
       </c>
       <c r="G20" s="12"/>
     </row>
@@ -3915,17 +3915,17 @@
         <v>46220</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>0.298611111111111</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.692361111111111</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">(D21-C21-E21)*24</f>
-        <v>8.95</v>
+        <v>7</v>
       </c>
       <c r="G21" s="12"/>
     </row>
@@ -3967,17 +3967,17 @@
         <v>46223</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>0.295138888888889</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.690972222222222</v>
+        <v>0.59375</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F24" s="11" t="n">
         <f aca="false">(D24-C24-E24)*24</f>
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="G24" s="12"/>
     </row>
@@ -3989,17 +3989,17 @@
         <v>46224</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.28125</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.629166666666667</v>
+        <v>0.586805555555556</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F25" s="11" t="n">
         <f aca="false">(D25-C25-E25)*24</f>
-        <v>7.85</v>
+        <v>6.5</v>
       </c>
       <c r="G25" s="12"/>
     </row>
@@ -4011,17 +4011,17 @@
         <v>46225</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.302083333333333</v>
+        <v>0.305555555555556</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.664583333333333</v>
+        <v>0.618055555555556</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F26" s="11" t="n">
         <f aca="false">(D26-C26-E26)*24</f>
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="G26" s="12"/>
     </row>
@@ -4033,17 +4033,17 @@
         <v>46226</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.716666666666667</v>
+        <v>0.600694444444444</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F27" s="11" t="n">
         <f aca="false">(D27-C27-E27)*24</f>
-        <v>9.45</v>
+        <v>6.75</v>
       </c>
       <c r="G27" s="12"/>
     </row>
@@ -4055,17 +4055,17 @@
         <v>46227</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.290277777777778</v>
+        <v>0.3125</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.648611111111111</v>
+        <v>0.614583333333333</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">(D28-C28-E28)*24</f>
-        <v>8.1</v>
+        <v>6.75</v>
       </c>
       <c r="G28" s="12"/>
     </row>
@@ -4107,17 +4107,17 @@
         <v>46230</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.305555555555556</v>
+        <v>0.295138888888889</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.688888888888889</v>
+        <v>0.597222222222222</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">(D31-C31-E31)*24</f>
-        <v>8.7</v>
+        <v>6.75</v>
       </c>
       <c r="G31" s="12"/>
     </row>
@@ -4129,17 +4129,17 @@
         <v>46231</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>0.286111111111111</v>
+        <v>0.309027777777778</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.704861111111111</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F32" s="11" t="n">
         <f aca="false">(D32-C32-E32)*24</f>
-        <v>9.3</v>
+        <v>6.75</v>
       </c>
       <c r="G32" s="12"/>
     </row>
@@ -4151,17 +4151,17 @@
         <v>46232</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.297222222222222</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.653472222222222</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F33" s="11" t="n">
         <f aca="false">(D33-C33-E33)*24</f>
-        <v>8.05</v>
+        <v>7</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4173,17 +4173,17 @@
         <v>46233</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.284722222222222</v>
+        <v>0.302083333333333</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.661805555555556</v>
+        <v>0.59375</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0.0208333333333333</v>
       </c>
       <c r="F34" s="11" t="n">
         <f aca="false">(D34-C34-E34)*24</f>
-        <v>8.55</v>
+        <v>6.5</v>
       </c>
       <c r="G34" s="12"/>
     </row>
@@ -4195,17 +4195,17 @@
         <v>46234</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>0.291666666666667</v>
+        <v>0.298611111111111</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.704166666666667</v>
+        <v>0.600694444444444</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.03125</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F35" s="11" t="n">
         <f aca="false">(D35-C35-E35)*24</f>
-        <v>9.15</v>
+        <v>6.75</v>
       </c>
       <c r="G35" s="12"/>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="F36" s="17" t="n">
         <f aca="false">SUM(F5:F35)</f>
-        <v>187.25</v>
+        <v>147.25</v>
       </c>
       <c r="G36" s="18" t="s">
         <v>22</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -702,7 +702,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>47.75</v>
+        <v>41.5</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>38</v>
@@ -731,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>47.25</v>
+        <v>41</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>38</v>
@@ -760,7 +760,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>34.25</v>
+        <v>30</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>30.5</v>
@@ -789,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>42.75</v>
+        <v>38.75</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>38</v>
@@ -818,7 +818,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>35.75</v>
+        <v>30.25</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>30.5</v>
@@ -847,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>33.75</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>30.5</v>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>44.25</v>
+        <v>38.25</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>38</v>
@@ -905,7 +905,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>44.75</v>
+        <v>38.25</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>38</v>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>34.75</v>
+        <v>24.75</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F13" s="8">
         <f>D13-E13</f>
@@ -963,7 +963,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>45</v>
+        <v>38.75</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>38</v>
@@ -992,7 +992,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>33.75</v>
+        <v>30</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>30.5</v>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>45</v>
+        <v>33.5</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F16" s="8">
         <f>D16-E16</f>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>34.75</v>
+        <v>23.75</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F17" s="8">
         <f>D17-E17</f>
@@ -1079,7 +1079,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>30.5</v>
@@ -1108,7 +1108,7 @@
         <v>5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>35.75</v>
+        <v>34.75</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>38</v>
@@ -1137,7 +1137,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>37</v>
+        <v>35.75</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>38</v>
@@ -1166,7 +1166,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>37</v>
+        <v>35.5</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>38</v>
@@ -1195,7 +1195,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>27.25</v>
+        <v>27.5</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>30.5</v>
@@ -1224,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>33.75</v>
+        <v>34.5</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>38</v>
@@ -1253,7 +1253,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>34</v>
+        <v>35.25</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>38</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>33.5</v>
+        <v>34.75</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>38</v>
@@ -1311,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>33.75</v>
+        <v>35</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>38</v>
@@ -1483,10 +1483,10 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
         <f>(D6-C6-E6)*24</f>
@@ -1507,7 +1507,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E7" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -1528,13 +1528,13 @@
         <v>46085</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.7118055555555556</v>
+        <v>0.6875</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
         <f>(D8-C8-E8)*24</f>
@@ -1555,10 +1555,10 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
         <f>(D9-C9-E9)*24</f>
@@ -1579,10 +1579,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F10" s="7">
         <f>(D10-C10-E10)*24</f>
@@ -1657,10 +1657,10 @@
         <v>0.3125</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
         <f>(D14-C14-E14)*24</f>
@@ -1681,7 +1681,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -1702,13 +1702,13 @@
         <v>46092</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
         <f>(D16-C16-E16)*24</f>
@@ -1726,13 +1726,13 @@
         <v>46093</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.71875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
         <f>(D17-C17-E17)*24</f>
@@ -1753,10 +1753,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F18" s="7">
         <f>(D18-C18-E18)*24</f>
@@ -1831,10 +1831,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
         <f>(D22-C22-E22)*24</f>
@@ -1855,10 +1855,10 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
         <f>(D23-C23-E23)*24</f>
@@ -1876,10 +1876,10 @@
         <v>46099</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>0.75</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E24" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -1907,10 +1907,10 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.7118055555555556</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
         <f>(D25-C25-E25)*24</f>
@@ -2004,10 +2004,10 @@
         <v>0.3125</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
         <f>(D30-C30-E30)*24</f>
@@ -2028,10 +2028,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
         <f>(D31-C31-E31)*24</f>
@@ -2052,7 +2052,7 @@
         <v>0.4895833333333333</v>
       </c>
       <c r="D32" s="19" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E32" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2077,10 +2077,10 @@
         <v>46107</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D33" s="19" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E33" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -2101,10 +2101,10 @@
         <v>46108</v>
       </c>
       <c r="C34" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E34" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -2179,13 +2179,13 @@
         <v>46111</v>
       </c>
       <c r="C38" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
         <f>(D38-C38-E38)*24</f>
@@ -2203,13 +2203,13 @@
         <v>46112</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.65625</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
         <f>(D39-C39-E39)*24</f>
@@ -2375,10 +2375,10 @@
         <v>46113</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.75</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2403,13 +2403,13 @@
         <v>46114</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
         <f>(D6-C6-E6)*24</f>
@@ -2523,13 +2523,13 @@
         <v>46119</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>0.3125</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
         <f>(D12-C12-E12)*24</f>
@@ -2550,7 +2550,7 @@
         <v>0.4965277777777778</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E13" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2575,13 +2575,13 @@
         <v>46121</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6875</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
         <f>(D14-C14-E14)*24</f>
@@ -2599,13 +2599,13 @@
         <v>46122</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
         <f>(D15-C15-E15)*24</f>
@@ -2677,13 +2677,13 @@
         <v>46125</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F19" s="7">
         <f>(D19-C19-E19)*24</f>
@@ -2701,13 +2701,13 @@
         <v>46126</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
         <f>(D20-C20-E20)*24</f>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2753,13 +2753,13 @@
         <v>46128</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
         <f>(D22-C22-E22)*24</f>
@@ -2780,10 +2780,10 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.75</v>
+        <v>0.65625</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
         <f>(D23-C23-E23)*24</f>
@@ -2855,13 +2855,13 @@
         <v>46132</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
         <f>(D27-C27-E27)*24</f>
@@ -2879,13 +2879,13 @@
         <v>46133</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>0.3125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
         <f>(D28-C28-E28)*24</f>
@@ -2906,7 +2906,7 @@
         <v>0.4930555555555556</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E29" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2931,13 +2931,13 @@
         <v>46135</v>
       </c>
       <c r="C30" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
         <f>(D30-C30-E30)*24</f>
@@ -2958,10 +2958,10 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.71875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
         <f>(D31-C31-E31)*24</f>
@@ -3036,10 +3036,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
         <f>(D35-C35-E35)*24</f>
@@ -3057,13 +3057,13 @@
         <v>46140</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
         <f>(D36-C36-E36)*24</f>
@@ -3072,30 +3072,21 @@
       <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="24" t="n">
         <v>46141</v>
       </c>
-      <c r="C37" s="19" t="n">
-        <v>0.5104166666666666</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F37" s="7">
-        <f>(D37-C37-E37)*24</f>
-        <v/>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP und Praktikum RT an der OTH</t>
         </is>
       </c>
     </row>
@@ -3112,10 +3103,10 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
         <f>(D38-C38-E38)*24</f>
@@ -3334,13 +3325,13 @@
         <v>46146</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
         <f>(D8-C8-E8)*24</f>
@@ -3361,10 +3352,10 @@
         <v>0.3125</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
         <f>(D9-C9-E9)*24</f>
@@ -3382,7 +3373,7 @@
         <v>46148</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>0.75</v>
@@ -3396,7 +3387,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3413,10 +3404,10 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
         <f>(D11-C11-E11)*24</f>
@@ -3434,13 +3425,13 @@
         <v>46150</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6840277777777778</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
         <f>(D12-C12-E12)*24</f>
@@ -3512,13 +3503,13 @@
         <v>46153</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
         <f>(D16-C16-E16)*24</f>
@@ -3539,10 +3530,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
         <f>(D17-C17-E17)*24</f>
@@ -3560,10 +3551,10 @@
         <v>46155</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E18" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -3574,7 +3565,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3610,10 +3601,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0.7152777777777778</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
         <f>(D20-C20-E20)*24</f>
@@ -3685,13 +3676,13 @@
         <v>46160</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
         <f>(D24-C24-E24)*24</f>
@@ -3712,10 +3703,10 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
         <f>(D25-C25-E25)*24</f>
@@ -3724,30 +3715,21 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="24" t="n">
         <v>46162</v>
       </c>
-      <c r="C26" s="19" t="n">
-        <v>0.5034722222222222</v>
-      </c>
-      <c r="D26" s="19" t="n">
-        <v>0.7326388888888888</v>
-      </c>
-      <c r="E26" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F26" s="7">
-        <f>(D26-C26-E26)*24</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP und Praktikum RT an der OTH</t>
         </is>
       </c>
     </row>
@@ -3764,10 +3746,10 @@
         <v>0.3125</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
         <f>(D27-C27-E27)*24</f>
@@ -3788,10 +3770,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0.75</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
         <f>(D28-C28-E28)*24</f>
@@ -3882,13 +3864,13 @@
         <v>46168</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D33" s="19" t="n">
-        <v>0.71875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
         <f>(D33-C33-E33)*24</f>
@@ -3897,30 +3879,21 @@
       <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="24" t="n">
         <v>46169</v>
       </c>
-      <c r="C34" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F34" s="7">
-        <f>(D34-C34-E34)*24</f>
-        <v/>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP und Praktikum RT an der OTH</t>
         </is>
       </c>
     </row>
@@ -3934,13 +3907,13 @@
         <v>46170</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
         <f>(D35-C35-E35)*24</f>
@@ -3958,13 +3931,13 @@
         <v>46171</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0.7430555555555556</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
         <f>(D36-C36-E36)*24</f>
@@ -4164,10 +4137,10 @@
         <v>46174</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4188,10 +4161,10 @@
         <v>46175</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4215,7 +4188,7 @@
         <v>0.4895833333333333</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="E7" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -4226,7 +4199,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4259,10 +4232,10 @@
         <v>46178</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>0.3125</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4337,10 +4310,10 @@
         <v>46181</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E13" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4361,10 +4334,10 @@
         <v>46182</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4385,10 +4358,10 @@
         <v>46183</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5034722222222222</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -4399,7 +4372,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4386,10 @@
         <v>46184</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.625</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E16" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4437,10 +4410,10 @@
         <v>46185</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.625</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E17" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4515,10 +4488,10 @@
         <v>46188</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.65625</v>
       </c>
       <c r="E21" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4539,10 +4512,10 @@
         <v>46189</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.625</v>
       </c>
       <c r="E22" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4563,10 +4536,10 @@
         <v>46190</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>0.4965277777777778</v>
+        <v>0.5</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.71875</v>
       </c>
       <c r="E23" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -4577,7 +4550,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4591,10 +4564,10 @@
         <v>46191</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E24" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4615,10 +4588,10 @@
         <v>46192</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>0.3125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E25" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4693,10 +4666,10 @@
         <v>46195</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E29" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4720,7 +4693,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E30" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4741,10 +4714,10 @@
         <v>46197</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.5</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="E31" s="19" t="n">
         <v>0.01041666666666667</v>
@@ -4755,7 +4728,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4745,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D32" s="19" t="n">
-        <v>0.65625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E32" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4793,10 +4766,10 @@
         <v>46199</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D33" s="19" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6875</v>
       </c>
       <c r="E33" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4874,7 +4847,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E37" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -4898,7 +4871,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E38" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5067,13 +5040,13 @@
         <v>46204</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>0.4930555555555556</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F5" s="7">
         <f>(D5-C5-E5)*24</f>
@@ -5081,7 +5054,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung 10:00–11:30, danach im Betrieb</t>
+          <t>danach Praktikum RT 15:30–17:00 an der OTH</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5071,7 @@
         <v>0.3125</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5199,7 +5172,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.5868055555555556</v>
       </c>
       <c r="E11" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5223,7 +5196,7 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0.6006944444444444</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E12" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5244,10 +5217,10 @@
         <v>46211</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E13" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5271,7 +5244,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5295,7 +5268,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.6006944444444444</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5373,7 +5346,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>0.6076388888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="E19" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5397,7 +5370,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E20" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5421,7 +5394,7 @@
         <v>0.3125</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E21" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5445,7 +5418,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E22" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5466,10 +5439,10 @@
         <v>46220</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E23" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5544,10 +5517,10 @@
         <v>46223</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.59375</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="E27" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5568,10 +5541,10 @@
         <v>46224</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0.5868055555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E28" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5592,10 +5565,10 @@
         <v>46225</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E29" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5616,10 +5589,10 @@
         <v>46226</v>
       </c>
       <c r="C30" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0.6006944444444444</v>
+        <v>0.65625</v>
       </c>
       <c r="E30" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5640,10 +5613,10 @@
         <v>46227</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.3125</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="E31" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5718,10 +5691,10 @@
         <v>46230</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="E35" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5742,10 +5715,10 @@
         <v>46231</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E36" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5766,10 +5739,10 @@
         <v>46232</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E37" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5790,10 +5763,10 @@
         <v>46233</v>
       </c>
       <c r="C38" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0.59375</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E38" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5814,10 +5787,10 @@
         <v>46234</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0.6006944444444444</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E39" s="19" t="n">
         <v>0.02083333333333333</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>30</v>
+        <v>24.5</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F7" s="8">
         <f>D7-E7</f>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>38.75</v>
+        <v>33.25</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F8" s="8">
         <f>D8-E8</f>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>30.25</v>
+        <v>24.75</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F9" s="8">
         <f>D9-E9</f>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>30</v>
+        <v>24.75</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F10" s="8">
         <f>D10-E10</f>
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>38.25</v>
+        <v>33</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F11" s="8">
         <f>D11-E11</f>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>38.25</v>
+        <v>32.75</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F12" s="8">
         <f>D12-E12</f>
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>38.75</v>
+        <v>33.25</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F14" s="8">
         <f>D14-E14</f>
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>30</v>
+        <v>24.75</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F15" s="8">
         <f>D15-E15</f>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>27.5</v>
+        <v>22.25</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>30.5</v>
+        <v>22.75</v>
       </c>
       <c r="F18" s="8">
         <f>D18-E18</f>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>34.75</v>
+        <v>29.75</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F19" s="8">
         <f>D19-E19</f>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>35.75</v>
+        <v>30.75</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F20" s="8">
         <f>D20-E20</f>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>35.5</v>
+        <v>30.25</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F21" s="8">
         <f>D21-E21</f>
@@ -1224,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>38</v>
@@ -1253,7 +1253,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>35.25</v>
+        <v>31.75</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>38</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>34.75</v>
+        <v>32</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>38</v>
@@ -1311,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>35</v>
+        <v>32.25</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>38</v>
@@ -1867,30 +1867,21 @@
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="24" t="n">
         <v>46099</v>
       </c>
-      <c r="C24" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D24" s="19" t="n">
-        <v>0.7395833333333334</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F24" s="7">
-        <f>(D24-C24-E24)*24</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -2040,30 +2031,21 @@
       <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="24" t="n">
         <v>46106</v>
       </c>
-      <c r="C32" s="19" t="n">
-        <v>0.4895833333333333</v>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>0.7291666666666666</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F32" s="7">
-        <f>(D32-C32-E32)*24</f>
-        <v/>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -2366,30 +2348,21 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="24" t="n">
         <v>46113</v>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>0.5069444444444444</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>0.7465277777777778</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F5" s="7">
-        <f>(D5-C5-E5)*24</f>
-        <v/>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -2538,30 +2511,21 @@
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="24" t="n">
         <v>46120</v>
       </c>
-      <c r="C13" s="19" t="n">
-        <v>0.4965277777777778</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>0.7256944444444444</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F13" s="7">
-        <f>(D13-C13-E13)*24</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -2716,30 +2680,21 @@
       <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="24" t="n">
         <v>46127</v>
       </c>
-      <c r="C21" s="19" t="n">
-        <v>0.5034722222222222</v>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>0.7326388888888888</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F21" s="7">
-        <f>(D21-C21-E21)*24</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -2894,30 +2849,21 @@
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="24" t="n">
         <v>46134</v>
       </c>
-      <c r="C29" s="19" t="n">
-        <v>0.4930555555555556</v>
-      </c>
-      <c r="D29" s="19" t="n">
-        <v>0.7326388888888888</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F29" s="7">
-        <f>(D29-C29-E29)*24</f>
-        <v/>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -3364,30 +3310,21 @@
       <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="24" t="n">
         <v>46148</v>
       </c>
-      <c r="C10" s="19" t="n">
-        <v>0.5104166666666666</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F10" s="7">
-        <f>(D10-C10-E10)*24</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -3542,30 +3479,21 @@
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="24" t="n">
         <v>46155</v>
       </c>
-      <c r="C18" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>0.7291666666666666</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F18" s="7">
-        <f>(D18-C18-E18)*24</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -4176,30 +4104,21 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="24" t="n">
         <v>46176</v>
       </c>
-      <c r="C7" s="19" t="n">
-        <v>0.4895833333333333</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F7" s="7">
-        <f>(D7-C7-E7)*24</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -4349,30 +4268,21 @@
       <c r="G14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="24" t="n">
         <v>46183</v>
       </c>
-      <c r="C15" s="19" t="n">
-        <v>0.5034722222222222</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F15" s="7">
-        <f>(D15-C15-E15)*24</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -4527,30 +4437,21 @@
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="24" t="n">
         <v>46190</v>
       </c>
-      <c r="C23" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F23" s="7">
-        <f>(D23-C23-E23)*24</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -4705,30 +4606,21 @@
       <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="24" t="n">
         <v>46197</v>
       </c>
-      <c r="C31" s="19" t="n">
-        <v>0.4895833333333333</v>
-      </c>
-      <c r="D31" s="19" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="E31" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
-      <c r="F31" s="7">
-        <f>(D31-C31-E31)*24</f>
-        <v/>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
         </is>
       </c>
     </row>
@@ -5241,19 +5133,23 @@
         <v>46212</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="F14" s="7">
         <f>(D14-C14-E14)*24</f>
         <v/>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Prüfung PRM bis 10:00, danach im Betrieb</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -5265,10 +5161,10 @@
         <v>46213</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.6006944444444444</v>
+        <v>0.625</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5343,10 +5239,10 @@
         <v>46216</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6006944444444444</v>
       </c>
       <c r="E19" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5367,10 +5263,10 @@
         <v>46217</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="E20" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5391,10 +5287,10 @@
         <v>46218</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>0.3125</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.625</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E21" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5415,10 +5311,10 @@
         <v>46219</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E22" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5439,19 +5335,23 @@
         <v>46220</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.65625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="F23" s="7">
         <f>(D23-C23-E23)*24</f>
         <v/>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Prüfung DA bis 10:00, danach im Betrieb</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -5517,19 +5417,23 @@
         <v>46223</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="F27" s="7">
         <f>(D27-C27-E27)*24</f>
         <v/>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Prüfung GAT bis 10:00, danach im Betrieb</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -5541,10 +5445,10 @@
         <v>46224</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E28" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5565,10 +5469,10 @@
         <v>46225</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="E29" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5589,10 +5493,10 @@
         <v>46226</v>
       </c>
       <c r="C30" s="19" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0.65625</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="E30" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5613,10 +5517,10 @@
         <v>46227</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E31" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5691,10 +5595,10 @@
         <v>46230</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E35" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5715,19 +5619,23 @@
         <v>46231</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.4618055555555556</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>0.6388888888888888</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="F36" s="7">
         <f>(D36-C36-E36)*24</f>
         <v/>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Prüfung SWV bis 10:00, danach im Betrieb</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -5739,10 +5647,10 @@
         <v>46232</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.65625</v>
       </c>
       <c r="E37" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5763,10 +5671,10 @@
         <v>46233</v>
       </c>
       <c r="C38" s="19" t="n">
-        <v>0.3159722222222222</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="E38" s="19" t="n">
         <v>0.02083333333333333</v>
@@ -5787,10 +5695,10 @@
         <v>46234</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E39" s="19" t="n">
         <v>0.02083333333333333</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -702,7 +702,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>38</v>
@@ -731,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>38</v>
@@ -760,7 +760,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>22.75</v>
@@ -789,7 +789,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>33.25</v>
+        <v>33.75</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>30.5</v>
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>24.75</v>
+        <v>25</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>22.75</v>
@@ -847,7 +847,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>24.75</v>
+        <v>24</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>22.75</v>
@@ -905,7 +905,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>32.75</v>
+        <v>32.25</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>30.5</v>
@@ -963,7 +963,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>33.25</v>
+        <v>32.5</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>30.5</v>
@@ -992,7 +992,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>24.75</v>
+        <v>23.75</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>22.75</v>
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>33.5</v>
+        <v>32</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>30.5</v>
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>23.75</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>22.75</v>
@@ -1195,7 +1195,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>30.5</v>
@@ -1224,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>32</v>
+        <v>31.75</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>38</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>32</v>
+        <v>31.75</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>38</v>
@@ -1483,13 +1483,13 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
-        <f>(D6-C6-E6)*24</f>
+        <f>(D6-C6-N(E6))*24</f>
         <v/>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F7" s="7">
-        <f>(D7-C7-E7)*24</f>
+        <f>(D7-C7-N(E7))*24</f>
         <v/>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>0.6875</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E8" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
-        <f>(D8-C8-E8)*24</f>
+        <f>(D8-C8-N(E8))*24</f>
         <v/>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
-        <f>(D9-C9-E9)*24</f>
+        <f>(D9-C9-N(E9))*24</f>
         <v/>
       </c>
       <c r="G9" s="6" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F10" s="7">
-        <f>(D10-C10-E10)*24</f>
+        <f>(D10-C10-N(E10))*24</f>
         <v/>
       </c>
       <c r="G10" s="6" t="inlineStr"/>
@@ -1657,13 +1657,13 @@
         <v>0.3125</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
-        <f>(D14-C14-E14)*24</f>
+        <f>(D14-C14-N(E14))*24</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
@@ -1681,13 +1681,13 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
-        <f>(D15-C15-E15)*24</f>
+        <f>(D15-C15-N(E15))*24</f>
         <v/>
       </c>
       <c r="G15" s="6" t="inlineStr"/>
@@ -1705,13 +1705,13 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.6840277777777778</v>
       </c>
       <c r="E16" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
-        <f>(D16-C16-E16)*24</f>
+        <f>(D16-C16-N(E16))*24</f>
         <v/>
       </c>
       <c r="G16" s="6" t="inlineStr"/>
@@ -1735,7 +1735,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
-        <f>(D17-C17-E17)*24</f>
+        <f>(D17-C17-N(E17))*24</f>
         <v/>
       </c>
       <c r="G17" s="6" t="inlineStr"/>
@@ -1753,13 +1753,13 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E18" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F18" s="7">
-        <f>(D18-C18-E18)*24</f>
+        <f>(D18-C18-N(E18))*24</f>
         <v/>
       </c>
       <c r="G18" s="6" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
-        <f>(D22-C22-E22)*24</f>
+        <f>(D22-C22-N(E22))*24</f>
         <v/>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -1855,13 +1855,13 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E23" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
-        <f>(D23-C23-E23)*24</f>
+        <f>(D23-C23-N(E23))*24</f>
         <v/>
       </c>
       <c r="G23" s="6" t="inlineStr"/>
@@ -1898,13 +1898,13 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E25" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
-        <f>(D25-C25-E25)*24</f>
+        <f>(D25-C25-N(E25))*24</f>
         <v/>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
-        <f>(D30-C30-E30)*24</f>
+        <f>(D30-C30-N(E30))*24</f>
         <v/>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -2019,13 +2019,13 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E31" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
-        <f>(D31-C31-E31)*24</f>
+        <f>(D31-C31-N(E31))*24</f>
         <v/>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
-        <f>(D33-C33-E33)*24</f>
+        <f>(D33-C33-N(E33))*24</f>
         <v/>
       </c>
       <c r="G33" s="6" t="inlineStr"/>
@@ -2086,13 +2086,13 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E34" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F34" s="7">
-        <f>(D34-C34-E34)*24</f>
+        <f>(D34-C34-N(E34))*24</f>
         <v/>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
-        <f>(D38-C38-E38)*24</f>
+        <f>(D38-C38-N(E38))*24</f>
         <v/>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -2188,13 +2188,13 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0.65625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E39" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
-        <f>(D39-C39-E39)*24</f>
+        <f>(D39-C39-N(E39))*24</f>
         <v/>
       </c>
       <c r="G39" s="6" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
-        <f>(D6-C6-E6)*24</f>
+        <f>(D6-C6-N(E6))*24</f>
         <v/>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -2499,13 +2499,13 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E12" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
-        <f>(D12-C12-E12)*24</f>
+        <f>(D12-C12-N(E12))*24</f>
         <v/>
       </c>
       <c r="G12" s="6" t="inlineStr"/>
@@ -2542,13 +2542,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.6875</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
-        <f>(D14-C14-E14)*24</f>
+        <f>(D14-C14-N(E14))*24</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
@@ -2566,13 +2566,13 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
-        <f>(D15-C15-E15)*24</f>
+        <f>(D15-C15-N(E15))*24</f>
         <v/>
       </c>
       <c r="G15" s="6" t="inlineStr"/>
@@ -2650,7 +2650,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F19" s="7">
-        <f>(D19-C19-E19)*24</f>
+        <f>(D19-C19-N(E19))*24</f>
         <v/>
       </c>
       <c r="G19" s="6" t="inlineStr"/>
@@ -2674,7 +2674,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
-        <f>(D20-C20-E20)*24</f>
+        <f>(D20-C20-N(E20))*24</f>
         <v/>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
-        <f>(D22-C22-E22)*24</f>
+        <f>(D22-C22-N(E22))*24</f>
         <v/>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
-        <f>(D23-C23-E23)*24</f>
+        <f>(D23-C23-N(E23))*24</f>
         <v/>
       </c>
       <c r="G23" s="6" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
-        <f>(D27-C27-E27)*24</f>
+        <f>(D27-C27-N(E27))*24</f>
         <v/>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
@@ -2837,13 +2837,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="E28" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
-        <f>(D28-C28-E28)*24</f>
+        <f>(D28-C28-N(E28))*24</f>
         <v/>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
@@ -2880,13 +2880,13 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="E30" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
-        <f>(D30-C30-E30)*24</f>
+        <f>(D30-C30-N(E30))*24</f>
         <v/>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -2910,7 +2910,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
-        <f>(D31-C31-E31)*24</f>
+        <f>(D31-C31-N(E31))*24</f>
         <v/>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
-        <f>(D35-C35-E35)*24</f>
+        <f>(D35-C35-N(E35))*24</f>
         <v/>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
-        <f>(D36-C36-E36)*24</f>
+        <f>(D36-C36-N(E36))*24</f>
         <v/>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
-        <f>(D38-C38-E38)*24</f>
+        <f>(D38-C38-N(E38))*24</f>
         <v/>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -3280,7 +3280,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
-        <f>(D8-C8-E8)*24</f>
+        <f>(D8-C8-N(E8))*24</f>
         <v/>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
@@ -3298,13 +3298,13 @@
         <v>0.3125</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
-        <f>(D9-C9-E9)*24</f>
+        <f>(D9-C9-N(E9))*24</f>
         <v/>
       </c>
       <c r="G9" s="6" t="inlineStr"/>
@@ -3341,13 +3341,13 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E11" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
-        <f>(D11-C11-E11)*24</f>
+        <f>(D11-C11-N(E11))*24</f>
         <v/>
       </c>
       <c r="G11" s="6" t="inlineStr"/>
@@ -3365,13 +3365,13 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0.6840277777777778</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E12" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
-        <f>(D12-C12-E12)*24</f>
+        <f>(D12-C12-N(E12))*24</f>
         <v/>
       </c>
       <c r="G12" s="6" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E16" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
-        <f>(D16-C16-E16)*24</f>
+        <f>(D16-C16-N(E16))*24</f>
         <v/>
       </c>
       <c r="G16" s="6" t="inlineStr"/>
@@ -3467,13 +3467,13 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.65625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E17" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
-        <f>(D17-C17-E17)*24</f>
+        <f>(D17-C17-N(E17))*24</f>
         <v/>
       </c>
       <c r="G17" s="6" t="inlineStr"/>
@@ -3529,13 +3529,13 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="E20" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
-        <f>(D20-C20-E20)*24</f>
+        <f>(D20-C20-N(E20))*24</f>
         <v/>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
@@ -3613,7 +3613,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
-        <f>(D24-C24-E24)*24</f>
+        <f>(D24-C24-N(E24))*24</f>
         <v/>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -3631,13 +3631,13 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E25" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
-        <f>(D25-C25-E25)*24</f>
+        <f>(D25-C25-N(E25))*24</f>
         <v/>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
         <v>0.3125</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="E27" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
-        <f>(D27-C27-E27)*24</f>
+        <f>(D27-C27-N(E27))*24</f>
         <v/>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
@@ -3698,13 +3698,13 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="E28" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
-        <f>(D28-C28-E28)*24</f>
+        <f>(D28-C28-N(E28))*24</f>
         <v/>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
@@ -3795,13 +3795,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D33" s="19" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E33" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
-        <f>(D33-C33-E33)*24</f>
+        <f>(D33-C33-N(E33))*24</f>
         <v/>
       </c>
       <c r="G33" s="6" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E35" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
-        <f>(D35-C35-E35)*24</f>
+        <f>(D35-C35-N(E35))*24</f>
         <v/>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
@@ -3862,13 +3862,13 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="E36" s="19" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
-        <f>(D36-C36-E36)*24</f>
+        <f>(D36-C36-N(E36))*24</f>
         <v/>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F5" s="7">
-        <f>(D5-C5-E5)*24</f>
+        <f>(D5-C5-N(E5))*24</f>
         <v/>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
-        <f>(D6-C6-E6)*24</f>
+        <f>(D6-C6-N(E6))*24</f>
         <v/>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -4160,7 +4160,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
-        <f>(D9-C9-E9)*24</f>
+        <f>(D9-C9-N(E9))*24</f>
         <v/>
       </c>
       <c r="G9" s="6" t="inlineStr"/>
@@ -4238,7 +4238,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
-        <f>(D13-C13-E13)*24</f>
+        <f>(D13-C13-N(E13))*24</f>
         <v/>
       </c>
       <c r="G13" s="6" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
-        <f>(D14-C14-E14)*24</f>
+        <f>(D14-C14-N(E14))*24</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
@@ -4305,7 +4305,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
-        <f>(D16-C16-E16)*24</f>
+        <f>(D16-C16-N(E16))*24</f>
         <v/>
       </c>
       <c r="G16" s="6" t="inlineStr"/>
@@ -4329,7 +4329,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
-        <f>(D17-C17-E17)*24</f>
+        <f>(D17-C17-N(E17))*24</f>
         <v/>
       </c>
       <c r="G17" s="6" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F21" s="7">
-        <f>(D21-C21-E21)*24</f>
+        <f>(D21-C21-N(E21))*24</f>
         <v/>
       </c>
       <c r="G21" s="6" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
-        <f>(D22-C22-E22)*24</f>
+        <f>(D22-C22-N(E22))*24</f>
         <v/>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
-        <f>(D24-C24-E24)*24</f>
+        <f>(D24-C24-N(E24))*24</f>
         <v/>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
-        <f>(D25-C25-E25)*24</f>
+        <f>(D25-C25-N(E25))*24</f>
         <v/>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F29" s="7">
-        <f>(D29-C29-E29)*24</f>
+        <f>(D29-C29-N(E29))*24</f>
         <v/>
       </c>
       <c r="G29" s="6" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
-        <f>(D30-C30-E30)*24</f>
+        <f>(D30-C30-N(E30))*24</f>
         <v/>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -4643,7 +4643,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F32" s="7">
-        <f>(D32-C32-E32)*24</f>
+        <f>(D32-C32-N(E32))*24</f>
         <v/>
       </c>
       <c r="G32" s="6" t="inlineStr"/>
@@ -4667,7 +4667,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
-        <f>(D33-C33-E33)*24</f>
+        <f>(D33-C33-N(E33))*24</f>
         <v/>
       </c>
       <c r="G33" s="6" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F37" s="7">
-        <f>(D37-C37-E37)*24</f>
+        <f>(D37-C37-N(E37))*24</f>
         <v/>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
@@ -4769,7 +4769,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
-        <f>(D38-C38-E38)*24</f>
+        <f>(D38-C38-N(E38))*24</f>
         <v/>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -4937,11 +4937,9 @@
       <c r="D5" s="19" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.02083333333333333</v>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="7">
-        <f>(D5-C5-E5)*24</f>
+        <f>(D5-C5-N(E5))*24</f>
         <v/>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -4969,7 +4967,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
-        <f>(D6-C6-E6)*24</f>
+        <f>(D6-C6-N(E6))*24</f>
         <v/>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -5070,7 +5068,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
-        <f>(D11-C11-E11)*24</f>
+        <f>(D11-C11-N(E11))*24</f>
         <v/>
       </c>
       <c r="G11" s="6" t="inlineStr"/>
@@ -5094,7 +5092,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
-        <f>(D12-C12-E12)*24</f>
+        <f>(D12-C12-N(E12))*24</f>
         <v/>
       </c>
       <c r="G12" s="6" t="inlineStr"/>
@@ -5118,7 +5116,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
-        <f>(D13-C13-E13)*24</f>
+        <f>(D13-C13-N(E13))*24</f>
         <v/>
       </c>
       <c r="G13" s="6" t="inlineStr"/>
@@ -5136,13 +5134,11 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="E14" s="5" t="n"/>
       <c r="F14" s="7">
-        <f>(D14-C14-E14)*24</f>
+        <f>(D14-C14-N(E14))*24</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -5170,7 +5166,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
-        <f>(D15-C15-E15)*24</f>
+        <f>(D15-C15-N(E15))*24</f>
         <v/>
       </c>
       <c r="G15" s="6" t="inlineStr"/>
@@ -5248,7 +5244,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F19" s="7">
-        <f>(D19-C19-E19)*24</f>
+        <f>(D19-C19-N(E19))*24</f>
         <v/>
       </c>
       <c r="G19" s="6" t="inlineStr"/>
@@ -5272,7 +5268,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
-        <f>(D20-C20-E20)*24</f>
+        <f>(D20-C20-N(E20))*24</f>
         <v/>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
@@ -5296,7 +5292,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F21" s="7">
-        <f>(D21-C21-E21)*24</f>
+        <f>(D21-C21-N(E21))*24</f>
         <v/>
       </c>
       <c r="G21" s="6" t="inlineStr"/>
@@ -5320,7 +5316,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
-        <f>(D22-C22-E22)*24</f>
+        <f>(D22-C22-N(E22))*24</f>
         <v/>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -5335,16 +5331,14 @@
         <v>46220</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>0.46875</v>
+        <v>0.4618055555555556</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
+        <v>0.6284722222222222</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
       <c r="F23" s="7">
-        <f>(D23-C23-E23)*24</f>
+        <f>(D23-C23-N(E23))*24</f>
         <v/>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -5420,13 +5414,11 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="E27" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="5" t="n"/>
       <c r="F27" s="7">
-        <f>(D27-C27-E27)*24</f>
+        <f>(D27-C27-N(E27))*24</f>
         <v/>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -5454,7 +5446,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
-        <f>(D28-C28-E28)*24</f>
+        <f>(D28-C28-N(E28))*24</f>
         <v/>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
@@ -5478,7 +5470,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F29" s="7">
-        <f>(D29-C29-E29)*24</f>
+        <f>(D29-C29-N(E29))*24</f>
         <v/>
       </c>
       <c r="G29" s="6" t="inlineStr"/>
@@ -5502,7 +5494,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
-        <f>(D30-C30-E30)*24</f>
+        <f>(D30-C30-N(E30))*24</f>
         <v/>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -5526,7 +5518,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
-        <f>(D31-C31-E31)*24</f>
+        <f>(D31-C31-N(E31))*24</f>
         <v/>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
@@ -5604,7 +5596,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
-        <f>(D35-C35-E35)*24</f>
+        <f>(D35-C35-N(E35))*24</f>
         <v/>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
@@ -5619,16 +5611,14 @@
         <v>46231</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.4618055555555556</v>
+        <v>0.4652777777777778</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="E36" s="19" t="n">
-        <v>0.01041666666666667</v>
-      </c>
+        <v>0.6319444444444444</v>
+      </c>
+      <c r="E36" s="5" t="n"/>
       <c r="F36" s="7">
-        <f>(D36-C36-E36)*24</f>
+        <f>(D36-C36-N(E36))*24</f>
         <v/>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -5656,7 +5646,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F37" s="7">
-        <f>(D37-C37-E37)*24</f>
+        <f>(D37-C37-N(E37))*24</f>
         <v/>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
@@ -5680,7 +5670,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
-        <f>(D38-C38-E38)*24</f>
+        <f>(D38-C38-N(E38))*24</f>
         <v/>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -5704,7 +5694,7 @@
         <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
-        <f>(D39-C39-E39)*24</f>
+        <f>(D39-C39-N(E39))*24</f>
         <v/>
       </c>
       <c r="G39" s="6" t="inlineStr"/>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Juli" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Wochenübersicht'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Wochenübersicht'!$A$1:$G$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'März'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'April'!$A$1:$G$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mai'!$A$1:$G$43</definedName>
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>25</v>
+        <v>28.75</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>22.75</v>
+        <v>30.5</v>
       </c>
       <c r="F9" s="8">
         <f>D9-E9</f>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>24</v>
+        <v>27.75</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>22.75</v>
+        <v>30.5</v>
       </c>
       <c r="F10" s="8">
         <f>D10-E10</f>
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>23.75</v>
+        <v>27.5</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22.75</v>
+        <v>30.5</v>
       </c>
       <c r="F15" s="8">
         <f>D15-E15</f>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>22.25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22.75</v>
+        <v>30.5</v>
       </c>
       <c r="F18" s="8">
         <f>D18-E18</f>
@@ -1359,6 +1359,13 @@
       <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Wochen über einen Monatswechsel sind hier vollständig zusammengefasst; in den Monatsblättern erscheinen sie anteilig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. An Vorlesungs-, Praktikums- und Prüfungstagen war nur ein Teil des Tages im Betrieb möglich.</t>
         </is>
       </c>
     </row>
@@ -2348,21 +2355,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="18" t="n">
         <v>46113</v>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C5" s="19" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7">
+        <f>(D5-C5-N(E5))*24</f>
+        <v/>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
         </is>
       </c>
     </row>
@@ -2511,21 +2525,28 @@
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="18" t="n">
         <v>46120</v>
       </c>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C13" s="19" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="7">
+        <f>(D13-C13-N(E13))*24</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
         </is>
       </c>
     </row>
@@ -3479,21 +3500,28 @@
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="18" t="n">
         <v>46155</v>
       </c>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C18" s="19" t="n">
+        <v>0.5069444444444444</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>0.6631944444444444</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="7">
+        <f>(D18-C18-N(E18))*24</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
         </is>
       </c>
     </row>
@@ -4104,21 +4132,28 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="18" t="n">
         <v>46176</v>
       </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C7" s="19" t="n">
+        <v>0.5138888888888888</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0.6701388888888888</v>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="7">
+        <f>(D7-C7-N(E7))*24</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
         </is>
       </c>
     </row>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>22.75</v>
+        <v>26.5</v>
       </c>
       <c r="F7" s="8">
         <f>D7-E7</f>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>33.75</v>
+        <v>37.75</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F8" s="8">
         <f>D8-E8</f>
@@ -818,10 +818,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>28.75</v>
+        <v>29</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="F9" s="8">
         <f>D9-E9</f>
@@ -847,10 +847,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>27.75</v>
+        <v>28</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="F10" s="8">
         <f>D10-E10</f>
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F11" s="8">
         <f>D11-E11</f>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>32.25</v>
+        <v>36.25</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F12" s="8">
         <f>D12-E12</f>
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>32.5</v>
+        <v>36.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F14" s="8">
         <f>D14-E14</f>
@@ -992,10 +992,10 @@
         <v>4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>27.5</v>
+        <v>27.75</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="F15" s="8">
         <f>D15-E15</f>
@@ -1079,10 +1079,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>26</v>
+        <v>26.25</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="F18" s="8">
         <f>D18-E18</f>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>29.75</v>
+        <v>33.75</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F19" s="8">
         <f>D19-E19</f>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>30.75</v>
+        <v>34.75</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F20" s="8">
         <f>D20-E20</f>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>30.25</v>
+        <v>34.25</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F21" s="8">
         <f>D21-E21</f>
@@ -1198,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
       <c r="F22" s="8">
         <f>D22-E22</f>
@@ -1227,7 +1227,7 @@
         <v>31.75</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>38</v>
+        <v>34.25</v>
       </c>
       <c r="F23" s="8">
         <f>D23-E23</f>
@@ -1256,7 +1256,7 @@
         <v>31.75</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>38</v>
+        <v>34.25</v>
       </c>
       <c r="F24" s="8">
         <f>D24-E24</f>
@@ -1285,7 +1285,7 @@
         <v>31.75</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>38</v>
+        <v>34.25</v>
       </c>
       <c r="F25" s="8">
         <f>D25-E25</f>
@@ -1314,7 +1314,7 @@
         <v>32.25</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>38</v>
+        <v>34.25</v>
       </c>
       <c r="F26" s="8">
         <f>D26-E26</f>
@@ -1365,7 +1365,7 @@
     <row r="30">
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. An Vorlesungs-, Praktikums- und Prüfungstagen war nur ein Teil des Tages im Betrieb möglich.</t>
+          <t>Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. Vorlesungs-, Praktikums- und Prüfungstage zählen als halber Tag, weil der Vormittag an der OTH war.</t>
         </is>
       </c>
     </row>
@@ -1874,21 +1874,28 @@
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="18" t="n">
         <v>46099</v>
       </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C24" s="19" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="7">
+        <f>(D24-C24-N(E24))*24</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2038,21 +2045,28 @@
       <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B32" s="24" t="n">
+      <c r="B32" s="18" t="n">
         <v>46106</v>
       </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="23" t="n"/>
-      <c r="G32" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C32" s="19" t="n">
+        <v>0.5069444444444444</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="7">
+        <f>(D32-C32-N(E32))*24</f>
+        <v/>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2364,10 +2378,10 @@
         <v>46113</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="7">
@@ -2376,7 +2390,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2551,7 @@
         <v>0.5104166666666666</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="7">
@@ -2546,7 +2560,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2701,21 +2715,28 @@
       <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="18" t="n">
         <v>46127</v>
       </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C21" s="19" t="n">
+        <v>0.5173611111111112</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>0.6840277777777778</v>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="7">
+        <f>(D21-C21-N(E21))*24</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2870,21 +2891,28 @@
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="18" t="n">
         <v>46134</v>
       </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C29" s="19" t="n">
+        <v>0.5069444444444444</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="7">
+        <f>(D29-C29-N(E29))*24</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3331,21 +3359,28 @@
       <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="18" t="n">
         <v>46148</v>
       </c>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C10" s="19" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="7">
+        <f>(D10-C10-N(E10))*24</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3509,10 +3544,10 @@
         <v>46155</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="7">
@@ -3521,7 +3556,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4141,10 +4176,10 @@
         <v>46176</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="7">
@@ -4153,7 +4188,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht</t>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4303,21 +4338,28 @@
       <c r="G14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="18" t="n">
         <v>46183</v>
       </c>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C15" s="19" t="n">
+        <v>0.5069444444444444</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="7">
+        <f>(D15-C15-N(E15))*24</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4472,21 +4514,28 @@
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="18" t="n">
         <v>46190</v>
       </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C23" s="19" t="n">
+        <v>0.5138888888888888</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="7">
+        <f>(D23-C23-N(E23))*24</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4641,21 +4690,28 @@
       <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B31" s="24" t="n">
+      <c r="B31" s="18" t="n">
         <v>46197</v>
       </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
-      <c r="G31" s="25" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30 an der OTH</t>
+      <c r="C31" s="19" t="n">
+        <v>0.5104166666666666</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="7">
+        <f>(D31-C31-N(E31))*24</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
         </is>
       </c>
     </row>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Juli" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Wochenübersicht'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Wochenübersicht'!$A$1:$G$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'März'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'April'!$A$1:$G$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mai'!$A$1:$G$43</definedName>
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="HH:MM"/>
     <numFmt numFmtId="167" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +106,11 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -181,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,7 +223,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -619,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1351,21 +1368,65 @@
     <row r="28">
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Ø je Woche</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Wochen über einen Monatswechsel sind hier vollständig zusammengefasst; in den Monatsblättern erscheinen sie anteilig.</t>
+          <t>Ø je Kalenderwoche</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. Vorlesungs-, Praktikums- und Prüfungstage zählen als halber Tag, weil der Vormittag an der OTH war.</t>
+          <t>Soll laut Vertrag</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>684</v>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>38,0 h/Woche × 18 Wochen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Ist laut Tätigkeitsnachweis</t>
+        </is>
+      </c>
+      <c r="D31" s="15">
+        <f>D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Differenz</t>
+        </is>
+      </c>
+      <c r="D32" s="18">
+        <f>D27-684.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Wochen über einen Monatswechsel sind hier vollständig zusammengefasst; in den Monatsblättern erscheinen sie anteilig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Spalte Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. Vorlesungs-, Praktikums- und Prüfungstage zählen als halber Tag, weil der Vormittag an der OTH war.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Ø je Kalenderwoche rechnet über alle 22 Wochen des Zeitraums, also einschließlich der Wochen mit Feiertag, Krankheit oder Hochschultag.</t>
         </is>
       </c>
     </row>
@@ -1459,19 +1520,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="20" t="n">
         <v>46082</v>
       </c>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
@@ -1483,16 +1544,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="22" t="n">
         <v>46083</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -1507,16 +1568,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="22" t="n">
         <v>46084</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F7" s="7">
@@ -1531,16 +1592,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="22" t="n">
         <v>46085</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="23" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
@@ -1555,16 +1616,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="22" t="n">
         <v>46086</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="23" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
@@ -1579,16 +1640,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="22" t="n">
         <v>46087</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F10" s="7">
@@ -1598,58 +1659,58 @@
       <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="20" t="n">
         <v>46088</v>
       </c>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="20" t="n">
         <v>46089</v>
       </c>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Summe KW 10</t>
         </is>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="26">
         <f>SUM(F6:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="20" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1657,16 +1718,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="22" t="n">
         <v>46090</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
@@ -1681,16 +1742,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="22" t="n">
         <v>46091</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
@@ -1705,16 +1766,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="22" t="n">
         <v>46092</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="23" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="23" t="n">
         <v>0.6840277777777778</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
@@ -1729,16 +1790,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="22" t="n">
         <v>46093</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="23" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
@@ -1753,16 +1814,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="22" t="n">
         <v>46094</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F18" s="7">
@@ -1772,58 +1833,58 @@
       <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="20" t="n">
         <v>46095</v>
       </c>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="20" t="n">
         <v>46096</v>
       </c>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n"/>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>Summe KW 11</t>
         </is>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="26">
         <f>SUM(F14:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="20" t="n"/>
+      <c r="G21" s="24" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1831,16 +1892,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="22" t="n">
         <v>46097</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -1855,16 +1916,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="22" t="n">
         <v>46098</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
@@ -1879,13 +1940,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="22" t="n">
         <v>46099</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="23" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="E24" s="5" t="n"/>
@@ -1905,16 +1966,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="22" t="n">
         <v>46100</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.6597222222222222</v>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
@@ -1924,77 +1985,77 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B26" s="24" t="n">
+      <c r="B26" s="28" t="n">
         <v>46101</v>
       </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>Krank</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="20" t="n">
         <v>46102</v>
       </c>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="20" t="n">
         <v>46103</v>
       </c>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>Summe KW 12</t>
         </is>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="26">
         <f>SUM(F22:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="20" t="n"/>
+      <c r="G29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2002,16 +2063,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="22" t="n">
         <v>46104</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E30" s="19" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -2026,16 +2087,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="22" t="n">
         <v>46105</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E31" s="19" t="n">
+      <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
@@ -2050,13 +2111,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="22" t="n">
         <v>46106</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="23" t="n">
         <v>0.5069444444444444</v>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
       <c r="E32" s="5" t="n"/>
@@ -2076,16 +2137,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="22" t="n">
         <v>46107</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="23" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E33" s="19" t="n">
+      <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
@@ -2100,16 +2161,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="22" t="n">
         <v>46108</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="D34" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E34" s="19" t="n">
+      <c r="E34" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F34" s="7">
@@ -2119,58 +2180,58 @@
       <c r="G34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="20" t="n">
         <v>46109</v>
       </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="20" t="n">
         <v>46110</v>
       </c>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="n"/>
-      <c r="B37" s="20" t="n"/>
-      <c r="C37" s="20" t="n"/>
-      <c r="D37" s="20" t="n"/>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="A37" s="24" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>Summe KW 13</t>
         </is>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="26">
         <f>SUM(F30:F36)</f>
         <v/>
       </c>
-      <c r="G37" s="20" t="n"/>
+      <c r="G37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2178,16 +2239,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="22" t="n">
         <v>46111</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="23" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D38" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -2202,16 +2263,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="22" t="n">
         <v>46112</v>
       </c>
-      <c r="C39" s="19" t="n">
+      <c r="C39" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E39" s="19" t="n">
+      <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
@@ -2221,20 +2282,20 @@
       <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n"/>
-      <c r="B40" s="20" t="n"/>
-      <c r="C40" s="20" t="n"/>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="25" t="inlineStr">
         <is>
           <t>Summe KW 14</t>
         </is>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="26">
         <f>SUM(F38:F39)</f>
         <v/>
       </c>
-      <c r="G40" s="26" t="inlineStr">
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
@@ -2250,28 +2311,28 @@
         <f>F13+F21+F29+F37+F40</f>
         <v/>
       </c>
-      <c r="G41" s="27" t="inlineStr">
+      <c r="G41" s="31" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="n"/>
-      <c r="B43" s="28" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="E43" s="28" t="n"/>
-      <c r="F43" s="28" t="n"/>
-      <c r="G43" s="28" t="n"/>
-      <c r="H43" s="28" t="n"/>
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E44" s="29" t="inlineStr">
+      <c r="E44" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -2374,13 +2435,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="22" t="n">
         <v>46113</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>0.5138888888888888</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>0.6805555555555556</v>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -2400,16 +2461,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="22" t="n">
         <v>46114</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -2419,96 +2480,96 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="28" t="n">
         <v>46115</v>
       </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>Karfreitag</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="20" t="n">
         <v>46116</v>
       </c>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="20" t="n">
         <v>46117</v>
       </c>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Summe KW 14</t>
         </is>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="26">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="28" t="n">
         <v>46118</v>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>Ostermontag</t>
         </is>
@@ -2520,16 +2581,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="22" t="n">
         <v>46119</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>0.6527777777777778</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
@@ -2544,13 +2605,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="22" t="n">
         <v>46120</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="23" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="E13" s="5" t="n"/>
@@ -2570,16 +2631,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="22" t="n">
         <v>46121</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
@@ -2594,16 +2655,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="22" t="n">
         <v>46122</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
@@ -2613,58 +2674,58 @@
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="20" t="n">
         <v>46123</v>
       </c>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="20" t="n">
         <v>46124</v>
       </c>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Summe KW 15</t>
         </is>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="26">
         <f>SUM(F11:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="20" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2672,16 +2733,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="22" t="n">
         <v>46125</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F19" s="7">
@@ -2696,16 +2757,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="22" t="n">
         <v>46126</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="23" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
@@ -2720,13 +2781,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="22" t="n">
         <v>46127</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="23" t="n">
         <v>0.5173611111111112</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="23" t="n">
         <v>0.6840277777777778</v>
       </c>
       <c r="E21" s="5" t="n"/>
@@ -2746,16 +2807,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="22" t="n">
         <v>46128</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -2770,16 +2831,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="22" t="n">
         <v>46129</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
@@ -2789,58 +2850,58 @@
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="20" t="n">
         <v>46130</v>
       </c>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="20" t="n">
         <v>46131</v>
       </c>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n"/>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>Summe KW 16</t>
         </is>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="26">
         <f>SUM(F19:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="20" t="n"/>
+      <c r="G26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2848,16 +2909,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="22" t="n">
         <v>46132</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
@@ -2872,16 +2933,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="22" t="n">
         <v>46133</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="23" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E28" s="19" t="n">
+      <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
@@ -2896,13 +2957,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="22" t="n">
         <v>46134</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="23" t="n">
         <v>0.5069444444444444</v>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
       <c r="E29" s="5" t="n"/>
@@ -2922,16 +2983,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="22" t="n">
         <v>46135</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.6631944444444444</v>
       </c>
-      <c r="E30" s="19" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -2946,16 +3007,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="22" t="n">
         <v>46136</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E31" s="19" t="n">
+      <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
@@ -2965,58 +3026,58 @@
       <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="20" t="n">
         <v>46137</v>
       </c>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="20" t="n">
         <v>46138</v>
       </c>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="n"/>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="25" t="inlineStr">
         <is>
           <t>Summe KW 17</t>
         </is>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="26">
         <f>SUM(F27:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="20" t="n"/>
+      <c r="G34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3024,16 +3085,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="22" t="n">
         <v>46139</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D35" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
@@ -3048,16 +3109,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="22" t="n">
         <v>46140</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="23" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
@@ -3067,19 +3128,19 @@
       <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B37" s="24" t="n">
+      <c r="B37" s="28" t="n">
         <v>46141</v>
       </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="29" t="inlineStr">
         <is>
           <t>Vorlesung PP und Praktikum RT an der OTH</t>
         </is>
@@ -3091,16 +3152,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="22" t="n">
         <v>46142</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D38" s="23" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -3110,20 +3171,20 @@
       <c r="G38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>Summe KW 18</t>
         </is>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="26">
         <f>SUM(F35:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="20" t="n"/>
+      <c r="G39" s="24" t="n"/>
     </row>
     <row r="40">
       <c r="E40" s="9" t="inlineStr">
@@ -3135,28 +3196,28 @@
         <f>F10+F18+F26+F34+F39</f>
         <v/>
       </c>
-      <c r="G40" s="27" t="inlineStr">
+      <c r="G40" s="31" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28" t="n"/>
+      <c r="A42" s="32" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="32" t="n"/>
+      <c r="E42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="32" t="n"/>
+      <c r="H42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -3254,57 +3315,57 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="28" t="n">
         <v>46143</v>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>Tag der Arbeit</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="20" t="n">
         <v>46144</v>
       </c>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="20" t="n">
         <v>46145</v>
       </c>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
@@ -3316,16 +3377,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="22" t="n">
         <v>46146</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
@@ -3340,16 +3401,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="22" t="n">
         <v>46147</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
@@ -3364,13 +3425,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="22" t="n">
         <v>46148</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -3390,16 +3451,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="22" t="n">
         <v>46149</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="23" t="n">
         <v>0.6388888888888888</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
@@ -3414,16 +3475,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="22" t="n">
         <v>46150</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
@@ -3433,58 +3494,58 @@
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="20" t="n">
         <v>46151</v>
       </c>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="20" t="n">
         <v>46152</v>
       </c>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n"/>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Summe KW 19</t>
         </is>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="26">
         <f>SUM(F8:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="20" t="n"/>
+      <c r="G15" s="24" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -3492,16 +3553,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="22" t="n">
         <v>46153</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="23" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
@@ -3516,16 +3577,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="22" t="n">
         <v>46154</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
@@ -3540,13 +3601,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="22" t="n">
         <v>46155</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="23" t="n">
         <v>0.5138888888888888</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.6805555555555556</v>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -3561,19 +3622,19 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Do</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="28" t="n">
         <v>46156</v>
       </c>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="29" t="inlineStr">
         <is>
           <t>Christi Himmelfahrt</t>
         </is>
@@ -3585,16 +3646,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="22" t="n">
         <v>46157</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.6423611111111112</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
@@ -3604,58 +3665,58 @@
       <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="20" t="n">
         <v>46158</v>
       </c>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="20" t="n">
         <v>46159</v>
       </c>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n"/>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Summe KW 20</t>
         </is>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="26">
         <f>SUM(F16:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="20" t="n"/>
+      <c r="G23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3663,16 +3724,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="22" t="n">
         <v>46160</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
@@ -3687,16 +3748,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="22" t="n">
         <v>46161</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.6388888888888888</v>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
@@ -3706,19 +3767,19 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B26" s="24" t="n">
+      <c r="B26" s="28" t="n">
         <v>46162</v>
       </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>Vorlesung PP und Praktikum RT an der OTH</t>
         </is>
@@ -3730,16 +3791,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="22" t="n">
         <v>46163</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
@@ -3754,16 +3815,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="22" t="n">
         <v>46164</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E28" s="19" t="n">
+      <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
@@ -3773,73 +3834,73 @@
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="20" t="n">
         <v>46165</v>
       </c>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="20" t="n">
         <v>46166</v>
       </c>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="n"/>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>Summe KW 21</t>
         </is>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="26">
         <f>SUM(F24:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="20" t="n"/>
+      <c r="G31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="B32" s="24" t="n">
+      <c r="B32" s="28" t="n">
         <v>46167</v>
       </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="23" t="n"/>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="29" t="inlineStr">
         <is>
           <t>Pfingstmontag</t>
         </is>
@@ -3851,16 +3912,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="22" t="n">
         <v>46168</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="23" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E33" s="19" t="n">
+      <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
@@ -3870,19 +3931,19 @@
       <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n">
+      <c r="B34" s="28" t="n">
         <v>46169</v>
       </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="25" t="inlineStr">
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>Vorlesung PP und Praktikum RT an der OTH</t>
         </is>
@@ -3894,16 +3955,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="22" t="n">
         <v>46170</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D35" s="23" t="n">
         <v>0.6284722222222222</v>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
@@ -3918,16 +3979,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="22" t="n">
         <v>46171</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="23" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="23" t="n">
         <v>0.6631944444444444</v>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
@@ -3937,58 +3998,58 @@
       <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="20" t="n">
         <v>46172</v>
       </c>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="20" t="n">
         <v>46173</v>
       </c>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>Summe KW 22</t>
         </is>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="26">
         <f>SUM(F32:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="20" t="n"/>
+      <c r="G39" s="24" t="n"/>
     </row>
     <row r="40">
       <c r="E40" s="9" t="inlineStr">
@@ -4000,28 +4061,28 @@
         <f>F15+F23+F31+F39</f>
         <v/>
       </c>
-      <c r="G40" s="27" t="inlineStr">
+      <c r="G40" s="31" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28" t="n"/>
+      <c r="A42" s="32" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="32" t="n"/>
+      <c r="E42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="32" t="n"/>
+      <c r="H42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -4124,16 +4185,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="22" t="n">
         <v>46174</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F5" s="7">
@@ -4148,16 +4209,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="22" t="n">
         <v>46175</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>0.6354166666666666</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -4172,13 +4233,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="22" t="n">
         <v>46176</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -4193,19 +4254,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Do</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="28" t="n">
         <v>46177</v>
       </c>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n"/>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Fronleichnam</t>
         </is>
@@ -4217,16 +4278,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="22" t="n">
         <v>46178</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="23" t="n">
         <v>0.6215277777777778</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
@@ -4236,58 +4297,58 @@
       <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="20" t="n">
         <v>46179</v>
       </c>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="20" t="n">
         <v>46180</v>
       </c>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n"/>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Summe KW 23</t>
         </is>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="26">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="20" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4295,16 +4356,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="22" t="n">
         <v>46181</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
@@ -4319,16 +4380,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="22" t="n">
         <v>46182</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>0.6493055555555556</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
@@ -4343,13 +4404,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="22" t="n">
         <v>46183</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>0.5069444444444444</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>0.6736111111111112</v>
       </c>
       <c r="E15" s="5" t="n"/>
@@ -4369,16 +4430,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="22" t="n">
         <v>46184</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="23" t="n">
         <v>0.6180555555555556</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
@@ -4393,16 +4454,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="22" t="n">
         <v>46185</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="23" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="23" t="n">
         <v>0.6284722222222222</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
@@ -4412,58 +4473,58 @@
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="20" t="n">
         <v>46186</v>
       </c>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="20" t="n">
         <v>46187</v>
       </c>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n"/>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Summe KW 24</t>
         </is>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="26">
         <f>SUM(F13:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="20" t="n"/>
+      <c r="G20" s="24" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4471,16 +4532,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="22" t="n">
         <v>46188</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F21" s="7">
@@ -4495,16 +4556,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="22" t="n">
         <v>46189</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.625</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -4519,13 +4580,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="22" t="n">
         <v>46190</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.5138888888888888</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.6805555555555556</v>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -4545,16 +4606,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="22" t="n">
         <v>46191</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
@@ -4569,16 +4630,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="22" t="n">
         <v>46192</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
@@ -4588,58 +4649,58 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="20" t="n">
         <v>46193</v>
       </c>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="20" t="n">
         <v>46194</v>
       </c>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n"/>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>Summe KW 25</t>
         </is>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="26">
         <f>SUM(F21:F27)</f>
         <v/>
       </c>
-      <c r="G28" s="20" t="n"/>
+      <c r="G28" s="24" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -4647,16 +4708,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="22" t="n">
         <v>46195</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="23" t="n">
         <v>0.6215277777777778</v>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F29" s="7">
@@ -4671,16 +4732,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="22" t="n">
         <v>46196</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.6145833333333334</v>
       </c>
-      <c r="E30" s="19" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -4695,13 +4756,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="22" t="n">
         <v>46197</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="23" t="n">
         <v>0.5104166666666666</v>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="23" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="E31" s="5" t="n"/>
@@ -4721,16 +4782,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="22" t="n">
         <v>46198</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E32" s="19" t="n">
+      <c r="E32" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F32" s="7">
@@ -4745,16 +4806,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="22" t="n">
         <v>46199</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="23" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E33" s="19" t="n">
+      <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
@@ -4764,58 +4825,58 @@
       <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="20" t="n">
         <v>46200</v>
       </c>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="20" t="n">
         <v>46201</v>
       </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="n"/>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="20" t="n"/>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="25" t="inlineStr">
         <is>
           <t>Summe KW 26</t>
         </is>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="26">
         <f>SUM(F29:F35)</f>
         <v/>
       </c>
-      <c r="G36" s="20" t="n"/>
+      <c r="G36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -4823,16 +4884,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="22" t="n">
         <v>46202</v>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D37" s="19" t="n">
+      <c r="D37" s="23" t="n">
         <v>0.6180555555555556</v>
       </c>
-      <c r="E37" s="19" t="n">
+      <c r="E37" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F37" s="7">
@@ -4847,16 +4908,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="22" t="n">
         <v>46203</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D38" s="23" t="n">
         <v>0.6319444444444444</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -4866,20 +4927,20 @@
       <c r="G38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>Summe KW 27</t>
         </is>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="26">
         <f>SUM(F37:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="26" t="inlineStr">
+      <c r="G39" s="30" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
@@ -4895,28 +4956,28 @@
         <f>F12+F20+F28+F36+F39</f>
         <v/>
       </c>
-      <c r="G40" s="27" t="inlineStr">
+      <c r="G40" s="31" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28" t="n"/>
+      <c r="A42" s="32" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="32" t="n"/>
+      <c r="E42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="32" t="n"/>
+      <c r="H42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -5019,13 +5080,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="22" t="n">
         <v>46204</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -5045,16 +5106,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="22" t="n">
         <v>46205</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -5064,77 +5125,77 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="28" t="n">
         <v>46206</v>
       </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>Krank</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="20" t="n">
         <v>46207</v>
       </c>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="20" t="n">
         <v>46208</v>
       </c>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Summe KW 27</t>
         </is>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="26">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
@@ -5146,16 +5207,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="22" t="n">
         <v>46209</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="23" t="n">
         <v>0.5868055555555556</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
@@ -5170,16 +5231,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="22" t="n">
         <v>46210</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
@@ -5194,16 +5255,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="22" t="n">
         <v>46211</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
@@ -5218,13 +5279,13 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="22" t="n">
         <v>46212</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>0.625</v>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -5244,16 +5305,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="22" t="n">
         <v>46213</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>0.625</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
@@ -5263,58 +5324,58 @@
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="20" t="n">
         <v>46214</v>
       </c>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="20" t="n">
         <v>46215</v>
       </c>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Summe KW 28</t>
         </is>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="26">
         <f>SUM(F11:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="20" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -5322,16 +5383,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="22" t="n">
         <v>46216</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="23" t="n">
         <v>0.6006944444444444</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F19" s="7">
@@ -5346,16 +5407,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="22" t="n">
         <v>46217</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
@@ -5370,16 +5431,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="22" t="n">
         <v>46218</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="23" t="n">
         <v>0.6284722222222222</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F21" s="7">
@@ -5394,16 +5455,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="22" t="n">
         <v>46219</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="23" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.625</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -5418,13 +5479,13 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="22" t="n">
         <v>46220</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.4618055555555556</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.6284722222222222</v>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -5439,58 +5500,58 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="20" t="n">
         <v>46221</v>
       </c>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="20" t="n">
         <v>46222</v>
       </c>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n"/>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>Summe KW 29</t>
         </is>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="26">
         <f>SUM(F19:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="20" t="n"/>
+      <c r="G26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5498,13 +5559,13 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="22" t="n">
         <v>46223</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="23" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="23" t="n">
         <v>0.625</v>
       </c>
       <c r="E27" s="5" t="n"/>
@@ -5524,16 +5585,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="22" t="n">
         <v>46224</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="23" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="23" t="n">
         <v>0.6145833333333334</v>
       </c>
-      <c r="E28" s="19" t="n">
+      <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
@@ -5548,16 +5609,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="22" t="n">
         <v>46225</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F29" s="7">
@@ -5572,16 +5633,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="22" t="n">
         <v>46226</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="23" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E30" s="19" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -5596,16 +5657,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="22" t="n">
         <v>46227</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="23" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="23" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="E31" s="19" t="n">
+      <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
@@ -5615,58 +5676,58 @@
       <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="20" t="n">
         <v>46228</v>
       </c>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="20" t="n">
         <v>46229</v>
       </c>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="n"/>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="25" t="inlineStr">
         <is>
           <t>Summe KW 30</t>
         </is>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="26">
         <f>SUM(F27:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="20" t="n"/>
+      <c r="G34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -5674,16 +5735,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="22" t="n">
         <v>46230</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D35" s="23" t="n">
         <v>0.6145833333333334</v>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
@@ -5698,13 +5759,13 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="22" t="n">
         <v>46231</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="23" t="n">
         <v>0.4652777777777778</v>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="23" t="n">
         <v>0.6319444444444444</v>
       </c>
       <c r="E36" s="5" t="n"/>
@@ -5724,16 +5785,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="22" t="n">
         <v>46232</v>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="23" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="D37" s="19" t="n">
+      <c r="D37" s="23" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E37" s="19" t="n">
+      <c r="E37" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F37" s="7">
@@ -5748,16 +5809,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="22" t="n">
         <v>46233</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="23" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D38" s="23" t="n">
         <v>0.5902777777777778</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -5772,16 +5833,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="22" t="n">
         <v>46234</v>
       </c>
-      <c r="C39" s="19" t="n">
+      <c r="C39" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="23" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E39" s="19" t="n">
+      <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
@@ -5791,20 +5852,20 @@
       <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n"/>
-      <c r="B40" s="20" t="n"/>
-      <c r="C40" s="20" t="n"/>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="25" t="inlineStr">
         <is>
           <t>Summe KW 31</t>
         </is>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="26">
         <f>SUM(F35:F39)</f>
         <v/>
       </c>
-      <c r="G40" s="20" t="n"/>
+      <c r="G40" s="24" t="n"/>
     </row>
     <row r="41">
       <c r="E41" s="9" t="inlineStr">
@@ -5816,28 +5877,28 @@
         <f>F10+F18+F26+F34+F40</f>
         <v/>
       </c>
-      <c r="G41" s="27" t="inlineStr">
+      <c r="G41" s="31" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="n"/>
-      <c r="B43" s="28" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="E43" s="28" t="n"/>
-      <c r="F43" s="28" t="n"/>
-      <c r="G43" s="28" t="n"/>
-      <c r="H43" s="28" t="n"/>
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E44" s="29" t="inlineStr">
+      <c r="E44" s="33" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -719,7 +719,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>38</v>
@@ -748,7 +748,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>42</v>
+        <v>47.25</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>38</v>
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>29</v>
+        <v>30.25</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>26.5</v>
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>37.75</v>
+        <v>40.5</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>34.25</v>
@@ -835,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>29</v>
+        <v>31.25</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>26.5</v>
@@ -864,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>28</v>
+        <v>30.75</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>26.5</v>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>37</v>
+        <v>39.5</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>34.25</v>
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>36.25</v>
+        <v>38</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>34.25</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>24.75</v>
+        <v>27</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22.75</v>
+        <v>26.5</v>
       </c>
       <c r="F13" s="8">
         <f>D13-E13</f>
@@ -980,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>36.5</v>
+        <v>38</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>34.25</v>
@@ -1009,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>27.75</v>
+        <v>32</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>26.5</v>
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>32</v>
+        <v>33.25</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>30.5</v>
+        <v>34.25</v>
       </c>
       <c r="F16" s="8">
         <f>D16-E16</f>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>23</v>
+        <v>26.5</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.75</v>
+        <v>26.5</v>
       </c>
       <c r="F17" s="8">
         <f>D17-E17</f>
@@ -1096,7 +1096,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>26.25</v>
+        <v>32.5</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>26.5</v>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>33.75</v>
+        <v>40</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>34.25</v>
@@ -1183,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>34.25</v>
+        <v>34</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>34.25</v>
@@ -1212,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>28</v>
+        <v>27.75</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>26.5</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>31.75</v>
+        <v>33</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>34.25</v>
@@ -1270,7 +1270,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>31.75</v>
+        <v>32.75</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>34.25</v>
@@ -1299,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>31.75</v>
+        <v>33</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>34.25</v>
@@ -1328,7 +1328,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>32.25</v>
+        <v>32.75</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>34.25</v>
@@ -1375,15 +1375,15 @@
     <row r="30">
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Soll laut Vertrag</t>
+          <t>Soll laut Vertrag § 6</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>684</v>
+        <v>775.25</v>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>38,0 h/Woche × 18 Wochen</t>
+          <t>102 Arbeitstage × 7,60 h (110 Werktage − 8 Feiertage/Krank)</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="D32" s="18">
-        <f>D27-684.0</f>
+        <f>D27-775.25</f>
         <v/>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
     <row r="35">
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Spalte Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. Vorlesungs-, Praktikums- und Prüfungstage zählen als halber Tag, weil der Vormittag an der OTH war.</t>
+          <t>Spalte Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. Vorlesungs-, Praktikums- und Prüfungstage zählen als halber Tag, weil der Vormittag an der OTH war. Der Vertrag selbst nennt keine Gesamtstundenzahl.</t>
         </is>
       </c>
     </row>
@@ -1551,10 +1551,10 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F6" s="7">
         <f>(D6-C6-N(E6))*24</f>
@@ -1575,10 +1575,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F7" s="7">
         <f>(D7-C7-N(E7))*24</f>
@@ -1599,10 +1599,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F8" s="7">
         <f>(D8-C8-N(E8))*24</f>
@@ -1620,13 +1620,13 @@
         <v>46086</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F9" s="7">
         <f>(D9-C9-N(E9))*24</f>
@@ -1647,10 +1647,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F10" s="7">
         <f>(D10-C10-N(E10))*24</f>
@@ -1725,10 +1725,10 @@
         <v>0.3125</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F14" s="7">
         <f>(D14-C14-N(E14))*24</f>
@@ -1749,10 +1749,10 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F15" s="7">
         <f>(D15-C15-N(E15))*24</f>
@@ -1773,7 +1773,7 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.6840277777777778</v>
+        <v>0.7048611111111112</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -1794,13 +1794,13 @@
         <v>46093</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F17" s="7">
         <f>(D17-C17-N(E17))*24</f>
@@ -1821,10 +1821,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F18" s="7">
         <f>(D18-C18-N(E18))*24</f>
@@ -1899,7 +1899,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -1923,7 +1923,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -1944,19 +1944,21 @@
         <v>46099</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="E24" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F24" s="7">
         <f>(D24-C24-N(E24))*24</f>
         <v/>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1975,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2070,10 +2072,10 @@
         <v>0.3125</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F30" s="7">
         <f>(D30-C30-N(E30))*24</f>
@@ -2094,7 +2096,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2115,19 +2117,21 @@
         <v>46106</v>
       </c>
       <c r="C32" s="23" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>0.6736111111111112</v>
-      </c>
-      <c r="E32" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F32" s="7">
         <f>(D32-C32-N(E32))*24</f>
         <v/>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2148,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2168,7 +2172,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E34" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2246,10 +2250,10 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E38" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F38" s="7">
         <f>(D38-C38-N(E38))*24</f>
@@ -2270,7 +2274,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2439,19 +2443,21 @@
         <v>46113</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="E5" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F5" s="7">
         <f>(D5-C5-N(E5))*24</f>
         <v/>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2474,7 @@
         <v>0.3229166666666667</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2588,7 +2594,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2609,19 +2615,21 @@
         <v>46120</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="E13" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F13" s="7">
         <f>(D13-C13-N(E13))*24</f>
         <v/>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2646,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2662,7 +2670,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2740,7 +2748,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2761,13 +2769,13 @@
         <v>46126</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0.3159722222222222</v>
+        <v>0.3125</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.75</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F20" s="7">
         <f>(D20-C20-N(E20))*24</f>
@@ -2785,19 +2793,21 @@
         <v>46127</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>0.5173611111111112</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0.6840277777777778</v>
-      </c>
-      <c r="E21" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F21" s="7">
         <f>(D21-C21-N(E21))*24</f>
         <v/>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2824,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2838,7 +2848,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2916,7 +2926,7 @@
         <v>0.3125</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2961,19 +2971,21 @@
         <v>46134</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.6736111111111112</v>
-      </c>
-      <c r="E29" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E29" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F29" s="7">
         <f>(D29-C29-N(E29))*24</f>
         <v/>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2990,7 +3002,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3014,7 +3026,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3092,10 +3104,10 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.71875</v>
       </c>
       <c r="E35" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F35" s="7">
         <f>(D35-C35-N(E35))*24</f>
@@ -3116,7 +3128,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3128,21 +3140,28 @@
       <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B37" s="28" t="n">
+      <c r="B37" s="22" t="n">
         <v>46141</v>
       </c>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="29" t="inlineStr">
-        <is>
-          <t>Vorlesung PP und Praktikum RT an der OTH</t>
+      <c r="C37" s="23" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="7">
+        <f>(D37-C37-N(E37))*24</f>
+        <v/>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 und Praktikum RT 15:30–17:00</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3178,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6701388888888888</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3384,7 +3403,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3408,7 +3427,7 @@
         <v>0.3125</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3429,19 +3448,21 @@
         <v>46148</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F10" s="7">
         <f>(D10-C10-N(E10))*24</f>
         <v/>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3479,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3482,7 +3503,7 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3557,13 +3578,13 @@
         <v>46153</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E16" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F16" s="7">
         <f>(D16-C16-N(E16))*24</f>
@@ -3584,7 +3605,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3605,19 +3626,21 @@
         <v>46155</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="E18" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F18" s="7">
         <f>(D18-C18-N(E18))*24</f>
         <v/>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3676,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3731,7 +3754,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3755,7 +3778,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3767,21 +3790,28 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="22" t="n">
         <v>46162</v>
       </c>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="29" t="inlineStr">
-        <is>
-          <t>Vorlesung PP und Praktikum RT an der OTH</t>
+      <c r="C26" s="23" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="7">
+        <f>(D26-C26-N(E26))*24</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 und Praktikum RT 15:30–17:00</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3852,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3919,10 +3949,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E33" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F33" s="7">
         <f>(D33-C33-N(E33))*24</f>
@@ -3931,21 +3961,28 @@
       <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n">
+      <c r="B34" s="22" t="n">
         <v>46169</v>
       </c>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="29" t="inlineStr">
-        <is>
-          <t>Vorlesung PP und Praktikum RT an der OTH</t>
+      <c r="C34" s="23" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="7">
+        <f>(D34-C34-N(E34))*24</f>
+        <v/>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Vorlesung PP 10:00–11:30 und Praktikum RT 15:30–17:00</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3999,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3986,7 +4023,7 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4192,7 +4229,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4216,7 +4253,7 @@
         <v>0.3229166666666667</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4237,19 +4274,21 @@
         <v>46176</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="E7" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F7" s="7">
         <f>(D7-C7-N(E7))*24</f>
         <v/>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4285,10 +4324,10 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F9" s="7">
         <f>(D9-C9-N(E9))*24</f>
@@ -4363,7 +4402,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4387,7 +4426,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4408,19 +4447,21 @@
         <v>46183</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.6736111111111112</v>
-      </c>
-      <c r="E15" s="5" t="n"/>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F15" s="7">
         <f>(D15-C15-N(E15))*24</f>
         <v/>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4437,10 +4478,10 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.7118055555555556</v>
       </c>
       <c r="E16" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F16" s="7">
         <f>(D16-C16-N(E16))*24</f>
@@ -4461,7 +4502,7 @@
         <v>0.3159722222222222</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4536,10 +4577,10 @@
         <v>46188</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4563,7 +4604,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4584,19 +4625,21 @@
         <v>46190</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="E23" s="5" t="n"/>
+        <v>0.625</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F23" s="7">
         <f>(D23-C23-N(E23))*24</f>
         <v/>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4656,7 @@
         <v>0.3125</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4634,10 +4677,10 @@
         <v>46192</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4715,7 +4758,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6006944444444444</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4760,19 +4803,21 @@
         <v>46197</v>
       </c>
       <c r="C31" s="23" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="E31" s="5" t="n"/>
+        <v>0.625</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>0.1041666666666667</v>
+      </c>
       <c r="F31" s="7">
         <f>(D31-C31-N(E31))*24</f>
         <v/>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4786,10 +4831,10 @@
         <v>46198</v>
       </c>
       <c r="C32" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E32" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4810,10 +4855,10 @@
         <v>46199</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4888,10 +4933,10 @@
         <v>46202</v>
       </c>
       <c r="C37" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.625</v>
       </c>
       <c r="E37" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4915,7 +4960,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5113,7 +5158,7 @@
         <v>0.3125</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5211,10 +5256,10 @@
         <v>46209</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.5868055555555556</v>
+        <v>0.625</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5259,10 +5304,10 @@
         <v>46211</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5309,7 +5354,7 @@
         <v>46213</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D15" s="23" t="n">
         <v>0.625</v>
@@ -5390,7 +5435,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.6006944444444444</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5411,10 +5456,10 @@
         <v>46217</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5438,7 +5483,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5483,10 +5528,10 @@
         <v>46220</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>0.4618055555555556</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.625</v>
       </c>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="7">
@@ -5589,10 +5634,10 @@
         <v>46224</v>
       </c>
       <c r="C28" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5613,10 +5658,10 @@
         <v>46225</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5640,7 +5685,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5661,10 +5706,10 @@
         <v>46227</v>
       </c>
       <c r="C31" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.625</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5742,7 +5787,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5763,10 +5808,10 @@
         <v>46231</v>
       </c>
       <c r="C36" s="23" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.625</v>
       </c>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="7">
@@ -5789,10 +5834,10 @@
         <v>46232</v>
       </c>
       <c r="C37" s="23" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
       <c r="E37" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5816,7 +5861,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5837,10 +5882,10 @@
         <v>46234</v>
       </c>
       <c r="C39" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -867,7 +867,7 @@
         <v>30.75</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>26.5</v>
+        <v>30.5</v>
       </c>
       <c r="F10" s="8">
         <f>D10-E10</f>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>39.5</v>
+        <v>39.75</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>34.25</v>
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>38</v>
+        <v>37.75</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>34.25</v>
@@ -2615,23 +2615,19 @@
         <v>46120</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
         <f>(D13-C13-N(E13))*24</f>
         <v/>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2643,10 +2639,10 @@
         <v>46121</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2667,10 +2663,10 @@
         <v>46122</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2745,13 +2741,13 @@
         <v>46125</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.75</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F19" s="7">
         <f>(D19-C19-N(E19))*24</f>
@@ -2769,13 +2765,13 @@
         <v>46126</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
         <f>(D20-C20-N(E20))*24</f>
@@ -2821,7 +2817,7 @@
         <v>46128</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D22" s="23" t="n">
         <v>0.625</v>
@@ -2845,10 +2841,10 @@
         <v>46129</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2923,10 +2919,10 @@
         <v>46132</v>
       </c>
       <c r="C27" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2947,10 +2943,10 @@
         <v>46133</v>
       </c>
       <c r="C28" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2999,10 +2995,10 @@
         <v>46135</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3023,10 +3019,10 @@
         <v>46136</v>
       </c>
       <c r="C31" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3101,10 +3097,10 @@
         <v>46139</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.71875</v>
+        <v>0.75</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.03125</v>
@@ -3125,10 +3121,10 @@
         <v>46140</v>
       </c>
       <c r="C36" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3175,10 +3171,10 @@
         <v>46142</v>
       </c>
       <c r="C38" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3400,10 +3396,10 @@
         <v>46146</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3125</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3424,10 +3420,10 @@
         <v>46147</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3476,10 +3472,10 @@
         <v>46149</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3500,10 +3496,10 @@
         <v>46150</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3578,10 +3574,10 @@
         <v>46153</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.75</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>0.03125</v>
@@ -3602,10 +3598,10 @@
         <v>46154</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3673,10 +3669,10 @@
         <v>46157</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3751,10 +3747,10 @@
         <v>46160</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3775,10 +3771,10 @@
         <v>46161</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3825,10 +3821,10 @@
         <v>46163</v>
       </c>
       <c r="C27" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3849,10 +3845,10 @@
         <v>46164</v>
       </c>
       <c r="C28" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3946,10 +3942,10 @@
         <v>46168</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.75</v>
+        <v>0.7118055555555556</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.03125</v>
@@ -3996,10 +3992,10 @@
         <v>46170</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4020,10 +4016,10 @@
         <v>46171</v>
       </c>
       <c r="C36" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.625</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4226,10 +4222,10 @@
         <v>46174</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4250,10 +4246,10 @@
         <v>46175</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4321,10 +4317,10 @@
         <v>46178</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3125</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.03125</v>
@@ -4399,10 +4395,10 @@
         <v>46181</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4423,10 +4419,10 @@
         <v>46182</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4475,10 +4471,10 @@
         <v>46184</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.7118055555555556</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>0.03125</v>
@@ -4499,10 +4495,10 @@
         <v>46185</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>0.3159722222222222</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4601,10 +4597,10 @@
         <v>46189</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4755,10 +4751,10 @@
         <v>46195</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.6006944444444444</v>
+        <v>0.59375</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4779,10 +4775,10 @@
         <v>46196</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4855,10 +4851,10 @@
         <v>46199</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4957,10 +4953,10 @@
         <v>46203</v>
       </c>
       <c r="C38" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.625</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5155,10 +5151,10 @@
         <v>46205</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6076388888888888</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5280,10 +5276,10 @@
         <v>46210</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.625</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5432,10 +5428,10 @@
         <v>46216</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5480,10 +5476,10 @@
         <v>46218</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.625</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5504,10 +5500,10 @@
         <v>46219</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5658,10 +5654,10 @@
         <v>46225</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.625</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5682,10 +5678,10 @@
         <v>46226</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.625</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5784,10 +5780,10 @@
         <v>46230</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5858,10 +5854,10 @@
         <v>46233</v>
       </c>
       <c r="C38" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.625</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5882,10 +5878,10 @@
         <v>46234</v>
       </c>
       <c r="C39" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -777,10 +777,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>30.25</v>
+        <v>32.5</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>26.5</v>
+        <v>30.5</v>
       </c>
       <c r="F7" s="8">
         <f>D7-E7</f>
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>40.5</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>34.25</v>
@@ -835,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>31.25</v>
+        <v>26.5</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>26.5</v>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>39.75</v>
+        <v>34.75</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>34.25</v>
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>37.75</v>
+        <v>32.75</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>34.25</v>
@@ -980,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>34.25</v>
@@ -1009,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>26.5</v>
@@ -1096,7 +1096,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>32.5</v>
+        <v>27.5</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>26.5</v>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>34.25</v>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>34.75</v>
+        <v>31.75</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>34.25</v>
@@ -1183,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>34.25</v>
@@ -1944,23 +1944,19 @@
         <v>46099</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E24" s="23" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
         <f>(D24-C24-N(E24))*24</f>
         <v/>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
-        </is>
-      </c>
+      <c r="G24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1972,13 +1968,13 @@
         <v>46100</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="23" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="F25" s="7">
         <f>(D25-C25-N(E25))*24</f>
@@ -2069,13 +2065,13 @@
         <v>46104</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.75</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>0.03125</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
         <f>(D30-C30-N(E30))*24</f>
@@ -2093,10 +2089,10 @@
         <v>46105</v>
       </c>
       <c r="C31" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2120,18 +2116,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
       <c r="F32" s="7">
         <f>(D32-C32-N(E32))*24</f>
         <v/>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2139,10 @@
         <v>46107</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2169,10 +2163,10 @@
         <v>46108</v>
       </c>
       <c r="C34" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="E34" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2247,10 +2241,10 @@
         <v>46111</v>
       </c>
       <c r="C38" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.7256944444444444</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.03125</v>
@@ -2271,10 +2265,10 @@
         <v>46112</v>
       </c>
       <c r="C39" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2446,18 +2440,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="7">
         <f>(D5-C5-N(E5))*24</f>
         <v/>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2471,10 +2463,10 @@
         <v>46114</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2591,10 +2583,10 @@
         <v>46119</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2615,10 +2607,10 @@
         <v>46120</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2639,10 +2631,10 @@
         <v>46121</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2663,10 +2655,10 @@
         <v>46122</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2741,10 +2733,10 @@
         <v>46125</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.75</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0.03125</v>
@@ -2765,10 +2757,10 @@
         <v>46126</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2792,18 +2784,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E21" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E21" s="5" t="n"/>
       <c r="F21" s="7">
         <f>(D21-C21-N(E21))*24</f>
         <v/>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2817,10 +2807,10 @@
         <v>46128</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2841,10 +2831,10 @@
         <v>46129</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2919,10 +2909,10 @@
         <v>46132</v>
       </c>
       <c r="C27" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0.6875</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2943,10 +2933,10 @@
         <v>46133</v>
       </c>
       <c r="C28" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.625</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2970,18 +2960,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E29" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E29" s="5" t="n"/>
       <c r="F29" s="7">
         <f>(D29-C29-N(E29))*24</f>
         <v/>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -2995,10 +2983,10 @@
         <v>46135</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3019,10 +3007,10 @@
         <v>46136</v>
       </c>
       <c r="C31" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3097,10 +3085,10 @@
         <v>46139</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.75</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.03125</v>
@@ -3121,10 +3109,10 @@
         <v>46140</v>
       </c>
       <c r="C36" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3157,7 +3145,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30 und Praktikum RT 15:30–17:00</t>
+          <t>Vorlesung PP 10:00–13:15 und Praktikum RT 15:30–17:00</t>
         </is>
       </c>
     </row>
@@ -3171,10 +3159,10 @@
         <v>46142</v>
       </c>
       <c r="C38" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3125</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3396,10 +3384,10 @@
         <v>46146</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3420,10 +3408,10 @@
         <v>46147</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3447,18 +3435,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="7">
         <f>(D10-C10-N(E10))*24</f>
         <v/>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3472,10 +3458,10 @@
         <v>46149</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.6631944444444444</v>
+        <v>0.6875</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3496,10 +3482,10 @@
         <v>46150</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3574,10 +3560,10 @@
         <v>46153</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>0.03125</v>
@@ -3598,10 +3584,10 @@
         <v>46154</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3625,18 +3611,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="7">
         <f>(D18-C18-N(E18))*24</f>
         <v/>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -3669,10 +3653,10 @@
         <v>46157</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3747,10 +3731,10 @@
         <v>46160</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3771,10 +3755,10 @@
         <v>46161</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D25" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E25" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3807,7 +3791,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30 und Praktikum RT 15:30–17:00</t>
+          <t>Vorlesung PP 10:00–13:15 und Praktikum RT 15:30–17:00</t>
         </is>
       </c>
     </row>
@@ -3821,10 +3805,10 @@
         <v>46163</v>
       </c>
       <c r="C27" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3845,10 +3829,10 @@
         <v>46164</v>
       </c>
       <c r="C28" s="23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3942,10 +3926,10 @@
         <v>46168</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.7118055555555556</v>
+        <v>0.7256944444444444</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.03125</v>
@@ -3978,7 +3962,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30 und Praktikum RT 15:30–17:00</t>
+          <t>Vorlesung PP 10:00–13:15 und Praktikum RT 15:30–17:00</t>
         </is>
       </c>
     </row>
@@ -3992,10 +3976,10 @@
         <v>46170</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0.3090277777777778</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4016,10 +4000,10 @@
         <v>46171</v>
       </c>
       <c r="C36" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4222,10 +4206,10 @@
         <v>46174</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4246,10 +4230,10 @@
         <v>46175</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>0.2986111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.6875</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4273,18 +4257,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="7">
         <f>(D7-C7-N(E7))*24</f>
         <v/>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4317,10 +4299,10 @@
         <v>46178</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.75</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.03125</v>
@@ -4395,10 +4377,10 @@
         <v>46181</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6284722222222222</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4419,10 +4401,10 @@
         <v>46182</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4446,18 +4428,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E15" s="5" t="n"/>
       <c r="F15" s="7">
         <f>(D15-C15-N(E15))*24</f>
         <v/>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4471,10 +4451,10 @@
         <v>46184</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.3159722222222222</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.71875</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>0.03125</v>
@@ -4495,10 +4475,10 @@
         <v>46185</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4624,18 +4604,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E23" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
       <c r="F23" s="7">
         <f>(D23-C23-N(E23))*24</f>
         <v/>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4649,10 +4627,10 @@
         <v>46191</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4751,10 +4729,10 @@
         <v>46195</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.59375</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4802,18 +4780,16 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E31" s="5" t="n"/>
       <c r="F31" s="7">
         <f>(D31-C31-N(E31))*24</f>
         <v/>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00–11:30, davor und danach im Betrieb</t>
+          <t>Vorlesung PP 10:00–13:15, danach nicht mehr im Betrieb</t>
         </is>
       </c>
     </row>
@@ -4851,10 +4827,10 @@
         <v>46199</v>
       </c>
       <c r="C33" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E33" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4953,10 +4929,10 @@
         <v>46203</v>
       </c>
       <c r="C38" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5151,10 +5127,10 @@
         <v>46205</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6076388888888888</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5276,10 +5252,10 @@
         <v>46210</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>0.3229166666666667</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5300,10 +5276,10 @@
         <v>46211</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5428,10 +5404,10 @@
         <v>46216</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6076388888888888</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5500,10 +5476,10 @@
         <v>46219</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5654,10 +5630,10 @@
         <v>46225</v>
       </c>
       <c r="C29" s="23" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5678,10 +5654,10 @@
         <v>46226</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5780,10 +5756,10 @@
         <v>46230</v>
       </c>
       <c r="C35" s="23" t="n">
-        <v>0.3125</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.625</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -5878,10 +5854,10 @@
         <v>46234</v>
       </c>
       <c r="C39" s="23" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6076388888888888</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>30.5</v>
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>33</v>
+        <v>35.25</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>34.25</v>
@@ -835,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>26.5</v>
+        <v>28</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>26.5</v>
@@ -864,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>30.75</v>
+        <v>33</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>30.5</v>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>34.75</v>
+        <v>37</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>34.25</v>
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>32.75</v>
+        <v>35</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>34.25</v>
@@ -951,7 +951,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>26.5</v>
@@ -980,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>33</v>
+        <v>35.25</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>34.25</v>
@@ -1009,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>26.5</v>
@@ -1038,7 +1038,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>33.25</v>
+        <v>35.5</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>34.25</v>
@@ -1067,7 +1067,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>26.5</v>
+        <v>28</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>26.5</v>
@@ -1096,7 +1096,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>27.5</v>
+        <v>28.25</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>26.5</v>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>35</v>
+        <v>36.5</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>34.25</v>
@@ -1899,7 +1899,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -1947,7 +1947,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2068,7 +2068,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2092,7 +2092,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2166,7 +2166,7 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="E34" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2268,7 +2268,7 @@
         <v>0.3229166666666667</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2466,7 +2466,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2586,7 +2586,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2634,7 +2634,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2658,7 +2658,7 @@
         <v>0.3159722222222222</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2760,7 +2760,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2810,7 +2810,7 @@
         <v>0.3125</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E22" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2834,7 +2834,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2936,7 +2936,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -2986,7 +2986,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="E30" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3010,7 +3010,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="E31" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3112,7 +3112,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3162,7 +3162,7 @@
         <v>0.3125</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3387,7 +3387,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3411,7 +3411,7 @@
         <v>0.3090277777777778</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3485,7 +3485,7 @@
         <v>0.3020833333333333</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3587,7 +3587,7 @@
         <v>0.3055555555555556</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6701388888888888</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3656,7 +3656,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6493055555555556</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3734,7 +3734,7 @@
         <v>0.3125</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E24" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3808,7 +3808,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3832,7 +3832,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E28" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -3979,7 +3979,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4003,7 +4003,7 @@
         <v>0.3229166666666667</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4209,7 +4209,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4380,7 +4380,7 @@
         <v>0.2951388888888889</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>0.6284722222222222</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>0.02083333333333333</v>
@@ -4478,7 +4478,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.02083333333333333</v>

--- a/hochschule/Hassine_3399727_Zeiterfassung.xlsx
+++ b/hochschule/Hassine_3399727_Zeiterfassung.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Juli" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Wochenübersicht'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Wochenübersicht'!$A$1:$G$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'März'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'April'!$A$1:$G$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mai'!$A$1:$G$43</definedName>
@@ -186,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,6 +234,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1410,21 +1414,77 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Hypothetisch: Feiertage/Krankheitstage als 8-Std.-Arbeitstage</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Ist laut Nachweis</t>
+        </is>
+      </c>
+      <c r="D35" s="15">
+        <f>D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>+ 6 Feiertage × 8,00 h</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>+ 2 Krankheitstage × 8,00 h</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Hypothetische Summe</t>
+        </is>
+      </c>
+      <c r="D38" s="20">
+        <f>D35+D36+D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Nur zur Information - Feiertage und Krankheitstage sind keine Arbeitszeit und werden im tatsächlichen Nachweis nicht als solche erfasst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Wochen über einen Monatswechsel sind hier vollständig zusammengefasst; in den Monatsblättern erscheinen sie anteilig.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="16" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Spalte Soll = 38,0 h/Woche, anteilig je Anwesenheitstag. Vorlesungs-, Praktikums- und Prüfungstage zählen als halber Tag, weil der Vormittag an der OTH war. Der Vertrag selbst nennt keine Gesamtstundenzahl.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="16" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Ø je Kalenderwoche rechnet über alle 22 Wochen des Zeitraums, also einschließlich der Wochen mit Feiertag, Krankheit oder Hochschultag.</t>
         </is>
@@ -1520,19 +1580,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="22" t="n">
         <v>46082</v>
       </c>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
@@ -1544,16 +1604,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="24" t="n">
         <v>46083</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.71875</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F6" s="7">
@@ -1568,16 +1628,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="24" t="n">
         <v>46084</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="25" t="n">
         <v>0.7395833333333334</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F7" s="7">
@@ -1592,16 +1652,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="24" t="n">
         <v>46085</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.75</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F8" s="7">
@@ -1616,16 +1676,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="24" t="n">
         <v>46086</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.75</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F9" s="7">
@@ -1640,16 +1700,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="24" t="n">
         <v>46087</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="25" t="n">
         <v>0.7256944444444444</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F10" s="7">
@@ -1659,58 +1719,58 @@
       <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="22" t="n">
         <v>46088</v>
       </c>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="22" t="n">
         <v>46089</v>
       </c>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="A13" s="26" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Summe KW 10</t>
         </is>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="28">
         <f>SUM(F6:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="24" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1718,16 +1778,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="24" t="n">
         <v>46090</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="25" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="25" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F14" s="7">
@@ -1742,16 +1802,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="24" t="n">
         <v>46091</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="25" t="n">
         <v>0.7326388888888888</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F15" s="7">
@@ -1766,16 +1826,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="24" t="n">
         <v>46092</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="25" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="25" t="n">
         <v>0.7048611111111112</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F16" s="7">
@@ -1790,16 +1850,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="24" t="n">
         <v>46093</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="25" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="25" t="n">
         <v>0.75</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F17" s="7">
@@ -1814,16 +1874,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="24" t="n">
         <v>46094</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="25" t="n">
         <v>0.7395833333333334</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F18" s="7">
@@ -1833,58 +1893,58 @@
       <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="22" t="n">
         <v>46095</v>
       </c>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="22" t="n">
         <v>46096</v>
       </c>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>Summe KW 11</t>
         </is>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="28">
         <f>SUM(F14:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="24" t="n"/>
+      <c r="G21" s="26" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1892,16 +1952,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="24" t="n">
         <v>46097</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="25" t="n">
         <v>0.6527777777777778</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -1916,16 +1976,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="24" t="n">
         <v>46098</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="25" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="25" t="n">
         <v>0.6597222222222222</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
@@ -1940,16 +2000,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="24" t="n">
         <v>46099</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="25" t="n">
         <v>0.6597222222222222</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
@@ -1964,16 +2024,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="24" t="n">
         <v>46100</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="25" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="25" t="n">
         <v>0.75</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F25" s="7">
@@ -1983,77 +2043,77 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="30" t="n">
         <v>46101</v>
       </c>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="31" t="inlineStr">
         <is>
           <t>Krank</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="22" t="n">
         <v>46102</v>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="22" t="n">
         <v>46103</v>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="n"/>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>Summe KW 12</t>
         </is>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="28">
         <f>SUM(F22:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="24" t="n"/>
+      <c r="G29" s="26" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2061,16 +2121,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="24" t="n">
         <v>46104</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="25" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -2085,16 +2145,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="24" t="n">
         <v>46105</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="25" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
@@ -2109,13 +2169,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="24" t="n">
         <v>46106</v>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E32" s="5" t="n"/>
@@ -2135,16 +2195,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="24" t="n">
         <v>46107</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="25" t="n">
         <v>0.6493055555555556</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
@@ -2159,16 +2219,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="24" t="n">
         <v>46108</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="25" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="25" t="n">
         <v>0.6631944444444444</v>
       </c>
-      <c r="E34" s="23" t="n">
+      <c r="E34" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F34" s="7">
@@ -2178,58 +2238,58 @@
       <c r="G34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="22" t="n">
         <v>46109</v>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="22" t="n">
         <v>46110</v>
       </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="n"/>
-      <c r="B37" s="24" t="n"/>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="24" t="n"/>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="A37" s="26" t="n"/>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>Summe KW 13</t>
         </is>
       </c>
-      <c r="F37" s="26">
+      <c r="F37" s="28">
         <f>SUM(F30:F36)</f>
         <v/>
       </c>
-      <c r="G37" s="24" t="n"/>
+      <c r="G37" s="26" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2237,16 +2297,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="24" t="n">
         <v>46111</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="25" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F38" s="7">
@@ -2261,16 +2321,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="24" t="n">
         <v>46112</v>
       </c>
-      <c r="C39" s="23" t="n">
+      <c r="C39" s="25" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="D39" s="23" t="n">
+      <c r="D39" s="25" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E39" s="23" t="n">
+      <c r="E39" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
@@ -2280,20 +2340,20 @@
       <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="24" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>Summe KW 14</t>
         </is>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="28">
         <f>SUM(F38:F39)</f>
         <v/>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
@@ -2309,28 +2369,28 @@
         <f>F13+F21+F29+F37+F40</f>
         <v/>
       </c>
-      <c r="G41" s="31" t="inlineStr">
+      <c r="G41" s="33" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n"/>
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="32" t="n"/>
-      <c r="H43" s="32" t="n"/>
+      <c r="A43" s="34" t="n"/>
+      <c r="B43" s="34" t="n"/>
+      <c r="C43" s="34" t="n"/>
+      <c r="E43" s="34" t="n"/>
+      <c r="F43" s="34" t="n"/>
+      <c r="G43" s="34" t="n"/>
+      <c r="H43" s="34" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E44" s="33" t="inlineStr">
+      <c r="E44" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -2433,13 +2493,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="24" t="n">
         <v>46113</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -2459,16 +2519,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="24" t="n">
         <v>46114</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.6527777777777778</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -2478,96 +2538,96 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="30" t="n">
         <v>46115</v>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t>Karfreitag</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <v>46116</v>
       </c>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="22" t="n">
         <v>46117</v>
       </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="24" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Summe KW 14</t>
         </is>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="28">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="30" t="n">
         <v>46118</v>
       </c>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t>Ostermontag</t>
         </is>
@@ -2579,16 +2639,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="24" t="n">
         <v>46119</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="25" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
@@ -2603,16 +2663,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="24" t="n">
         <v>46120</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="25" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.6597222222222222</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
@@ -2627,16 +2687,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="24" t="n">
         <v>46121</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="25" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
@@ -2651,16 +2711,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="24" t="n">
         <v>46122</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="25" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="25" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
@@ -2670,58 +2730,58 @@
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="22" t="n">
         <v>46123</v>
       </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="19" t="n"/>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="22" t="n">
         <v>46124</v>
       </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Summe KW 15</t>
         </is>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="28">
         <f>SUM(F11:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="24" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2729,16 +2789,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="24" t="n">
         <v>46125</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="25" t="n">
         <v>0.7395833333333334</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F19" s="7">
@@ -2753,16 +2813,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="24" t="n">
         <v>46126</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="25" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
@@ -2777,13 +2837,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="24" t="n">
         <v>46127</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E21" s="5" t="n"/>
@@ -2803,16 +2863,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="24" t="n">
         <v>46128</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="25" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="25" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -2827,16 +2887,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="24" t="n">
         <v>46129</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="25" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F23" s="7">
@@ -2846,58 +2906,58 @@
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="22" t="n">
         <v>46130</v>
       </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="22" t="n">
         <v>46131</v>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Summe KW 16</t>
         </is>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="28">
         <f>SUM(F19:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="24" t="n"/>
+      <c r="G26" s="26" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2905,16 +2965,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="24" t="n">
         <v>46132</v>
       </c>
-      <c r="C27" s="23" t="n">
+      <c r="C27" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="25" t="n">
         <v>0.6527777777777778</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
@@ -2929,16 +2989,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="24" t="n">
         <v>46133</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="25" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
@@ -2953,13 +3013,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="24" t="n">
         <v>46134</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E29" s="5" t="n"/>
@@ -2979,16 +3039,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="24" t="n">
         <v>46135</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="25" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -3003,16 +3063,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="24" t="n">
         <v>46136</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="25" t="n">
         <v>0.6979166666666666</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
@@ -3022,58 +3082,58 @@
       <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="22" t="n">
         <v>46137</v>
       </c>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
+      <c r="B33" s="22" t="n">
         <v>46138</v>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>Summe KW 17</t>
         </is>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="28">
         <f>SUM(F27:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="24" t="n"/>
+      <c r="G34" s="26" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3081,16 +3141,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="24" t="n">
         <v>46139</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="25" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="25" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="E35" s="23" t="n">
+      <c r="E35" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F35" s="7">
@@ -3105,16 +3165,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="24" t="n">
         <v>46140</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="25" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E36" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
@@ -3129,13 +3189,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="24" t="n">
         <v>46141</v>
       </c>
-      <c r="C37" s="23" t="n">
+      <c r="C37" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E37" s="5" t="n"/>
@@ -3155,16 +3215,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="24" t="n">
         <v>46142</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="25" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="25" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -3174,20 +3234,20 @@
       <c r="G38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="n"/>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="A39" s="26" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>Summe KW 18</t>
         </is>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="28">
         <f>SUM(F35:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="24" t="n"/>
+      <c r="G39" s="26" t="n"/>
     </row>
     <row r="40">
       <c r="E40" s="9" t="inlineStr">
@@ -3199,28 +3259,28 @@
         <f>F10+F18+F26+F34+F39</f>
         <v/>
       </c>
-      <c r="G40" s="31" t="inlineStr">
+      <c r="G40" s="33" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n"/>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="32" t="n"/>
-      <c r="H42" s="32" t="n"/>
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="34" t="n"/>
+      <c r="G42" s="34" t="n"/>
+      <c r="H42" s="34" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E43" s="33" t="inlineStr">
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -3318,57 +3378,57 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="30" t="n">
         <v>46143</v>
       </c>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t>Tag der Arbeit</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="22" t="n">
         <v>46144</v>
       </c>
-      <c r="C6" s="19" t="n"/>
-      <c r="D6" s="19" t="n"/>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="22" t="n">
         <v>46145</v>
       </c>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
@@ -3380,16 +3440,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="24" t="n">
         <v>46146</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.6493055555555556</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F8" s="7">
@@ -3404,16 +3464,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="24" t="n">
         <v>46147</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="25" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.6736111111111112</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F9" s="7">
@@ -3428,13 +3488,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="24" t="n">
         <v>46148</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -3454,16 +3514,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="24" t="n">
         <v>46149</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="25" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
@@ -3478,16 +3538,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="24" t="n">
         <v>46150</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="25" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
@@ -3497,58 +3557,58 @@
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="22" t="n">
         <v>46151</v>
       </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="22" t="n">
         <v>46152</v>
       </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n"/>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="A15" s="26" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Summe KW 19</t>
         </is>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="28">
         <f>SUM(F8:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="24" t="n"/>
+      <c r="G15" s="26" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -3556,16 +3616,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="24" t="n">
         <v>46153</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="25" t="n">
         <v>0.7361111111111112</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F16" s="7">
@@ -3580,16 +3640,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="24" t="n">
         <v>46154</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="25" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="25" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
@@ -3604,13 +3664,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="24" t="n">
         <v>46155</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -3625,19 +3685,19 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Do</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="30" t="n">
         <v>46156</v>
       </c>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="29" t="inlineStr">
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="31" t="inlineStr">
         <is>
           <t>Christi Himmelfahrt</t>
         </is>
@@ -3649,16 +3709,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="24" t="n">
         <v>46157</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="25" t="n">
         <v>0.6493055555555556</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
@@ -3668,58 +3728,58 @@
       <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="22" t="n">
         <v>46158</v>
       </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="22" t="n">
         <v>46159</v>
       </c>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n"/>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="n"/>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Summe KW 20</t>
         </is>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="28">
         <f>SUM(F16:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="24" t="n"/>
+      <c r="G23" s="26" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3727,16 +3787,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="24" t="n">
         <v>46160</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="25" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="25" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
@@ -3751,16 +3811,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="24" t="n">
         <v>46161</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="25" t="n">
         <v>0.65625</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
@@ -3775,13 +3835,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="24" t="n">
         <v>46162</v>
       </c>
-      <c r="C26" s="23" t="n">
+      <c r="C26" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E26" s="5" t="n"/>
@@ -3801,16 +3861,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="24" t="n">
         <v>46163</v>
       </c>
-      <c r="C27" s="23" t="n">
+      <c r="C27" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="25" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F27" s="7">
@@ -3825,16 +3885,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="24" t="n">
         <v>46164</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="25" t="n">
         <v>0.6597222222222222</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
@@ -3844,73 +3904,73 @@
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="22" t="n">
         <v>46165</v>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="22" t="n">
         <v>46166</v>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="n"/>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="n"/>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>Summe KW 21</t>
         </is>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="28">
         <f>SUM(F24:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="24" t="n"/>
+      <c r="G31" s="26" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B32" s="30" t="n">
         <v>46167</v>
       </c>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="29" t="inlineStr">
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="29" t="n"/>
+      <c r="G32" s="31" t="inlineStr">
         <is>
           <t>Pfingstmontag</t>
         </is>
@@ -3922,16 +3982,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="24" t="n">
         <v>46168</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="25" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="25" t="n">
         <v>0.7256944444444444</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F33" s="7">
@@ -3946,13 +4006,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="24" t="n">
         <v>46169</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E34" s="5" t="n"/>
@@ -3972,16 +4032,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="24" t="n">
         <v>46170</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="25" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E35" s="23" t="n">
+      <c r="E35" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
@@ -3996,16 +4056,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="24" t="n">
         <v>46171</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="25" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="25" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E36" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F36" s="7">
@@ -4015,58 +4075,58 @@
       <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="22" t="n">
         <v>46172</v>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="21" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="22" t="n">
         <v>46173</v>
       </c>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="19" t="n"/>
-      <c r="F38" s="19" t="n"/>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="n"/>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="A39" s="26" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>Summe KW 22</t>
         </is>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="28">
         <f>SUM(F32:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="24" t="n"/>
+      <c r="G39" s="26" t="n"/>
     </row>
     <row r="40">
       <c r="E40" s="9" t="inlineStr">
@@ -4078,28 +4138,28 @@
         <f>F15+F23+F31+F39</f>
         <v/>
       </c>
-      <c r="G40" s="31" t="inlineStr">
+      <c r="G40" s="33" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n"/>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="32" t="n"/>
-      <c r="H42" s="32" t="n"/>
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="34" t="n"/>
+      <c r="G42" s="34" t="n"/>
+      <c r="H42" s="34" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E43" s="33" t="inlineStr">
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -4202,16 +4262,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="24" t="n">
         <v>46174</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.6527777777777778</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F5" s="7">
@@ -4226,16 +4286,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="24" t="n">
         <v>46175</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.6875</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -4250,13 +4310,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="24" t="n">
         <v>46176</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -4271,19 +4331,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Do</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="30" t="n">
         <v>46177</v>
       </c>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>Fronleichnam</t>
         </is>
@@ -4295,16 +4355,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="24" t="n">
         <v>46178</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="25" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.7430555555555556</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F9" s="7">
@@ -4314,58 +4374,58 @@
       <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <v>46179</v>
       </c>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="22" t="n">
         <v>46180</v>
       </c>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n"/>
-      <c r="B12" s="24" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Summe KW 23</t>
         </is>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="28">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="24" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4373,16 +4433,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="24" t="n">
         <v>46181</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.6597222222222222</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
@@ -4397,16 +4457,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="24" t="n">
         <v>46182</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="25" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="25" t="n">
         <v>0.6701388888888888</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F14" s="7">
@@ -4421,13 +4481,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="24" t="n">
         <v>46183</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E15" s="5" t="n"/>
@@ -4447,16 +4507,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="24" t="n">
         <v>46184</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="25" t="n">
         <v>0.71875</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.03125</v>
       </c>
       <c r="F16" s="7">
@@ -4471,16 +4531,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="24" t="n">
         <v>46185</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="25" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F17" s="7">
@@ -4490,58 +4550,58 @@
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="22" t="n">
         <v>46186</v>
       </c>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="22" t="n">
         <v>46187</v>
       </c>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="n"/>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Summe KW 24</t>
         </is>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="28">
         <f>SUM(F13:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="24" t="n"/>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4549,16 +4609,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="24" t="n">
         <v>46188</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F21" s="7">
@@ -4573,16 +4633,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="24" t="n">
         <v>46189</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -4597,13 +4657,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="24" t="n">
         <v>46190</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -4623,16 +4683,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="24" t="n">
         <v>46191</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="25" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F24" s="7">
@@ -4647,16 +4707,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="24" t="n">
         <v>46192</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F25" s="7">
@@ -4666,58 +4726,58 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="22" t="n">
         <v>46193</v>
       </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="22" t="n">
         <v>46194</v>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="n"/>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>Summe KW 25</t>
         </is>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="28">
         <f>SUM(F21:F27)</f>
         <v/>
       </c>
-      <c r="G28" s="24" t="n"/>
+      <c r="G28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -4725,16 +4785,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="24" t="n">
         <v>46195</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="25" t="n">
         <v>0.6041666666666666</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F29" s="7">
@@ -4749,16 +4809,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="24" t="n">
         <v>46196</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -4773,13 +4833,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="24" t="n">
         <v>46197</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="25" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E31" s="5" t="n"/>
@@ -4799,16 +4859,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="24" t="n">
         <v>46198</v>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E32" s="23" t="n">
+      <c r="E32" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F32" s="7">
@@ -4823,16 +4883,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="24" t="n">
         <v>46199</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="25" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F33" s="7">
@@ -4842,58 +4902,58 @@
       <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="22" t="n">
         <v>46200</v>
       </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="22" t="n">
         <v>46201</v>
       </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="n"/>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="A36" s="26" t="n"/>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>Summe KW 26</t>
         </is>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="28">
         <f>SUM(F29:F35)</f>
         <v/>
       </c>
-      <c r="G36" s="24" t="n"/>
+      <c r="G36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -4901,16 +4961,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="24" t="n">
         <v>46202</v>
       </c>
-      <c r="C37" s="23" t="n">
+      <c r="C37" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E37" s="23" t="n">
+      <c r="E37" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F37" s="7">
@@ -4925,16 +4985,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="24" t="n">
         <v>46203</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="25" t="n">
         <v>0.6180555555555556</v>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -4944,20 +5004,20 @@
       <c r="G38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="n"/>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="A39" s="26" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>Summe KW 27</t>
         </is>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="28">
         <f>SUM(F37:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="30" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
@@ -4973,28 +5033,28 @@
         <f>F12+F20+F28+F36+F39</f>
         <v/>
       </c>
-      <c r="G40" s="31" t="inlineStr">
+      <c r="G40" s="33" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n"/>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="32" t="n"/>
-      <c r="H42" s="32" t="n"/>
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="34" t="n"/>
+      <c r="G42" s="34" t="n"/>
+      <c r="H42" s="34" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E43" s="33" t="inlineStr">
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
@@ -5097,13 +5157,13 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="24" t="n">
         <v>46204</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="25" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -5123,16 +5183,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="24" t="n">
         <v>46205</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.6215277777777778</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F6" s="7">
@@ -5142,77 +5202,77 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="30" t="n">
         <v>46206</v>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t>Krank</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <v>46207</v>
       </c>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="22" t="n">
         <v>46208</v>
       </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="24" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Summe KW 27</t>
         </is>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="28">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>anteilig – Woche reicht in den Nachbarmonat</t>
         </is>
@@ -5224,16 +5284,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="24" t="n">
         <v>46209</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F11" s="7">
@@ -5248,16 +5308,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="24" t="n">
         <v>46210</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="25" t="n">
         <v>0.6041666666666666</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F12" s="7">
@@ -5272,16 +5332,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="24" t="n">
         <v>46211</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.6215277777777778</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F13" s="7">
@@ -5296,13 +5356,13 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="24" t="n">
         <v>46212</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="25" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="25" t="n">
         <v>0.625</v>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -5322,16 +5382,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="24" t="n">
         <v>46213</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F15" s="7">
@@ -5341,58 +5401,58 @@
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="22" t="n">
         <v>46214</v>
       </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="19" t="n"/>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="22" t="n">
         <v>46215</v>
       </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Summe KW 28</t>
         </is>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="28">
         <f>SUM(F11:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="24" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -5400,16 +5460,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="24" t="n">
         <v>46216</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="25" t="n">
         <v>0.6076388888888888</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F19" s="7">
@@ -5424,16 +5484,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="24" t="n">
         <v>46217</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F20" s="7">
@@ -5448,16 +5508,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="24" t="n">
         <v>46218</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F21" s="7">
@@ -5472,16 +5532,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="24" t="n">
         <v>46219</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="25" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F22" s="7">
@@ -5496,13 +5556,13 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="24" t="n">
         <v>46220</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="25" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="25" t="n">
         <v>0.625</v>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -5517,58 +5577,58 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="22" t="n">
         <v>46221</v>
       </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="22" t="n">
         <v>46222</v>
       </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Summe KW 29</t>
         </is>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="28">
         <f>SUM(F19:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="24" t="n"/>
+      <c r="G26" s="26" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5576,13 +5636,13 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="24" t="n">
         <v>46223</v>
       </c>
-      <c r="C27" s="23" t="n">
+      <c r="C27" s="25" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="25" t="n">
         <v>0.625</v>
       </c>
       <c r="E27" s="5" t="n"/>
@@ -5602,16 +5662,16 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="24" t="n">
         <v>46224</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F28" s="7">
@@ -5626,16 +5686,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="24" t="n">
         <v>46225</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="25" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="25" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F29" s="7">
@@ -5650,16 +5710,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="24" t="n">
         <v>46226</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="25" t="n">
         <v>0.6145833333333334</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F30" s="7">
@@ -5674,16 +5734,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="24" t="n">
         <v>46227</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F31" s="7">
@@ -5693,58 +5753,58 @@
       <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="22" t="n">
         <v>46228</v>
       </c>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
+      <c r="B33" s="22" t="n">
         <v>46229</v>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>Wochenende</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>Summe KW 30</t>
         </is>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="28">
         <f>SUM(F27:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="24" t="n"/>
+      <c r="G34" s="26" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -5752,16 +5812,16 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="24" t="n">
         <v>46230</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="25" t="n">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="25" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="E35" s="23" t="n">
+      <c r="E35" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F35" s="7">
@@ -5776,13 +5836,13 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="24" t="n">
         <v>46231</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="25" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="25" t="n">
         <v>0.625</v>
       </c>
       <c r="E36" s="5" t="n"/>
@@ -5802,16 +5862,16 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="24" t="n">
         <v>46232</v>
       </c>
-      <c r="C37" s="23" t="n">
+      <c r="C37" s="25" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E37" s="23" t="n">
+      <c r="E37" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F37" s="7">
@@ -5826,16 +5886,16 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="24" t="n">
         <v>46233</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="25" t="n">
         <v>0.3020833333333333</v>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="25" t="n">
         <v>0.625</v>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F38" s="7">
@@ -5850,16 +5910,16 @@
           <t>Fr</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="24" t="n">
         <v>46234</v>
       </c>
-      <c r="C39" s="23" t="n">
+      <c r="C39" s="25" t="n">
         <v>0.2951388888888889</v>
       </c>
-      <c r="D39" s="23" t="n">
+      <c r="D39" s="25" t="n">
         <v>0.6076388888888888</v>
       </c>
-      <c r="E39" s="23" t="n">
+      <c r="E39" s="25" t="n">
         <v>0.02083333333333333</v>
       </c>
       <c r="F39" s="7">
@@ -5869,20 +5929,20 @@
       <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="24" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>Summe KW 31</t>
         </is>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="28">
         <f>SUM(F35:F39)</f>
         <v/>
       </c>
-      <c r="G40" s="24" t="n"/>
+      <c r="G40" s="26" t="n"/>
     </row>
     <row r="41">
       <c r="E41" s="9" t="inlineStr">
@@ -5894,28 +5954,28 @@
         <f>F10+F18+F26+F34+F40</f>
         <v/>
       </c>
-      <c r="G41" s="31" t="inlineStr">
+      <c r="G41" s="33" t="inlineStr">
         <is>
           <t>Stunden netto im Monat</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n"/>
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="32" t="n"/>
-      <c r="H43" s="32" t="n"/>
+      <c r="A43" s="34" t="n"/>
+      <c r="B43" s="34" t="n"/>
+      <c r="C43" s="34" t="n"/>
+      <c r="E43" s="34" t="n"/>
+      <c r="F43" s="34" t="n"/>
+      <c r="G43" s="34" t="n"/>
+      <c r="H43" s="34" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift Praktikant</t>
         </is>
       </c>
-      <c r="E44" s="33" t="inlineStr">
+      <c r="E44" s="35" t="inlineStr">
         <is>
           <t>Datum, Unterschrift und Stempel des Betriebes</t>
         </is>
